--- a/Ritam_Bhattachrya_RedBus/Epic3.xlsx
+++ b/Ritam_Bhattachrya_RedBus/Epic3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ritam\Programming\Capgemini_Sprint\Ritam_Bhattachrya_RedBus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D9FF3B2-DFD9-477F-937E-513989D1DD57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56EFCB2E-625B-4593-951E-C025BCB3EC46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" tabRatio="500" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" tabRatio="500" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Train Search &amp; Filter" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="Test Cases" sheetId="4" r:id="rId4"/>
     <sheet name="RTM" sheetId="5" r:id="rId5"/>
     <sheet name="Defect Report" sheetId="6" r:id="rId6"/>
+    <sheet name="Test Execution Summary" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Test Cases'!$A$2:$K$2</definedName>
@@ -26,314 +27,16 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Train Search &amp; Filter'!$A$1:$C$1</definedName>
   </definedNames>
   <calcPr calcId="0" iterateDelta="1E-4"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="333">
-  <si>
-    <t>Issue Type</t>
-  </si>
-  <si>
-    <t>Summary</t>
-  </si>
-  <si>
-    <t>Priority</t>
-  </si>
-  <si>
-    <t>Epic</t>
-  </si>
-  <si>
-    <t>Bus Search and Filter Functionality</t>
-  </si>
-  <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t>Story</t>
-  </si>
-  <si>
-    <t>User searches trains between stations</t>
-  </si>
-  <si>
-    <t>Sub-story</t>
-  </si>
-  <si>
-    <t>Enter source and destination station</t>
-  </si>
-  <si>
-    <t>Validate same source and destination</t>
-  </si>
-  <si>
-    <t>Select journey date</t>
-  </si>
-  <si>
-    <t>Enable free cancellation filter in search</t>
-  </si>
-  <si>
-    <t>User applies filters to bus results</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>Filter by class (Sleeper, AC 3-tier, AC 2-tier, etc.)</t>
-  </si>
-  <si>
-    <t>Filter by quota (General, Ladies, Tatkal)</t>
-  </si>
-  <si>
-    <t>Filter by AC / Non-AC</t>
-  </si>
-  <si>
-    <t>Clear all applied filters</t>
-  </si>
-  <si>
-    <t>User sorts bus search results</t>
-  </si>
-  <si>
-    <t>Sort by price (low to high / high to low)</t>
-  </si>
-  <si>
-    <t>Sort by duration</t>
-  </si>
-  <si>
-    <t>Sort by departure time</t>
-  </si>
-  <si>
-    <t>Sort by arrival time</t>
-  </si>
-  <si>
-    <t>Module 3: Bus Search &amp; Filter</t>
-  </si>
-  <si>
-    <t>Item</t>
-  </si>
-  <si>
-    <t>Count</t>
-  </si>
-  <si>
-    <t>Total Epics</t>
-  </si>
-  <si>
-    <t>Total Stories</t>
-  </si>
-  <si>
-    <t>Total Sub-stories</t>
-  </si>
-  <si>
-    <t>High Priority Items</t>
-  </si>
-  <si>
-    <t>Medium Priority Items</t>
-  </si>
-  <si>
-    <t>Low Priority Items</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="362">
+  <si>
+    <t>TC ID</t>
   </si>
   <si>
     <t>Test Scenario ID</t>
-  </si>
-  <si>
-    <t>Requirement ID</t>
-  </si>
-  <si>
-    <t>Test Scenario Description</t>
-  </si>
-  <si>
-    <t>Type of Testing</t>
-  </si>
-  <si>
-    <t>Possible No. of Test Cases</t>
-  </si>
-  <si>
-    <t>Test Case Details</t>
-  </si>
-  <si>
-    <t>TS_Train_Search_001</t>
-  </si>
-  <si>
-    <t>REQ_Train_Search_001</t>
-  </si>
-  <si>
-    <t>Verify source and destination station entry</t>
-  </si>
-  <si>
-    <t>Functional Testing</t>
-  </si>
-  <si>
-    <t>1. To validate both source and destination left blank
-2. To validate search results load when both source and destination are correctly filled
-3. To validate source and destination filled using autocomplete and search results load
-4. To validate behaviour when source is valid and destination is invalid/wrong</t>
-  </si>
-  <si>
-    <t>TS_Train_Search_002</t>
-  </si>
-  <si>
-    <t>REQ_Train_Search_002</t>
-  </si>
-  <si>
-    <t>Verify validation when source and destination are the same</t>
-  </si>
-  <si>
-    <t>1. Validate error shown when source equals destination.
-2. Validate Search button is blocked on same-station entry.
-3. Validate error clears when destination is changed.</t>
-  </si>
-  <si>
-    <t>TS_Train_Search_003</t>
-  </si>
-  <si>
-    <t>REQ_Train_Search_003</t>
-  </si>
-  <si>
-    <t>Verify journey date selection behaviour</t>
-  </si>
-  <si>
-    <t>1. Validate date picker opens on clicking date field.
-2. Validate past dates are disabled and cannot be selected.
-3. Validate today's date is selectable.
-4. Validate tomorrow's date can be selected.
-5. Validate selected date is displayed correctly in the field.</t>
-  </si>
-  <si>
-    <t>TS_Train_Search_004</t>
-  </si>
-  <si>
-    <t>REQ_Train_Search_004</t>
-  </si>
-  <si>
-    <t>Verify free cancellation toggle in search</t>
-  </si>
-  <si>
-    <t>1. Validate free cancellation toggle is visible on search screen.
-2. Validate clicking toggle enables the filter (turns ON).
-3. Validate results show only free-cancellation trains when ON.
-4. Validate disabling toggle restores the full results.</t>
-  </si>
-  <si>
-    <t>TS_Train_Filter_001</t>
-  </si>
-  <si>
-    <t>REQ_Train_Filter_001</t>
-  </si>
-  <si>
-    <t>Verify filter by train class (Sleeper, AC 3-tier, AC 2-tier, etc.)</t>
-  </si>
-  <si>
-    <t>1. Validate all class options are listed (Sleeper, AC 3-tier, AC 2-tier, 1st AC).
-2. Validate selecting a single class filters results to that class only.
-3. Validate multi-class selection shows combined results.
-4. Validate deselecting a class removes it from filter.
-5. Validate no-results message when no trains match.</t>
-  </si>
-  <si>
-    <t>TS_Train_Filter_002</t>
-  </si>
-  <si>
-    <t>REQ_Train_Filter_002</t>
-  </si>
-  <si>
-    <t>Verify filter by quota (General, Ladies, Tatkal)</t>
-  </si>
-  <si>
-    <t>1. Validate General, Ladies, Tatkal quota options are available.
-2. Validate General quota shows correct availability.
-3. Validate Tatkal quota reflects Tatkal pricing.
-4. Validate Ladies quota shows berths with ladies quota.</t>
-  </si>
-  <si>
-    <t>TS_Train_Filter_003</t>
-  </si>
-  <si>
-    <t>REQ_Train_Filter_003</t>
-  </si>
-  <si>
-    <t>Verify AC / Non-AC top filter</t>
-  </si>
-  <si>
-    <t>1. Validate AC filter shows only AC class trains (1A, 2A, 3A, CC).
-2. Validate Non-AC filter shows only non-AC trains (Sleeper, 2S).
-3. Validate selecting both returns all available trains.</t>
-  </si>
-  <si>
-    <t>TS_Train_Filter_004</t>
-  </si>
-  <si>
-    <t>REQ_Train_Filter_004</t>
-  </si>
-  <si>
-    <t>Verify clear all filters functionality</t>
-  </si>
-  <si>
-    <t>1. Validate 'Clear All' button is visible when filters are applied.
-2. Validate clicking 'Clear All' removes all active filters at once.
-3. Validate results revert to full unfiltered list after clearing.</t>
-  </si>
-  <si>
-    <t>TS_Train_Sort_001</t>
-  </si>
-  <si>
-    <t>REQ_Train_Sort_001</t>
-  </si>
-  <si>
-    <t>Verify sort by price (low to high / high to low)</t>
-  </si>
-  <si>
-    <t>1. Validate 'Sort by Price' option is available in the sort menu.
-2. Validate 'Low to High' lists cheapest fare train first.
-3. Validate 'High to Low' lists most expensive fare train first.
-4. Validate sort updates the list immediately.</t>
-  </si>
-  <si>
-    <t>TS_Train_Sort_002</t>
-  </si>
-  <si>
-    <t>REQ_Train_Sort_002</t>
-  </si>
-  <si>
-    <t>Verify sort by journey duration</t>
-  </si>
-  <si>
-    <t>1. Validate ascending sort lists shortest journey train first.
-2. Validate descending sort lists longest journey train first.
-3. Validate trains with equal duration maintain consistent order.</t>
-  </si>
-  <si>
-    <t>TS_Train_Sort_003</t>
-  </si>
-  <si>
-    <t>REQ_Train_Sort_003</t>
-  </si>
-  <si>
-    <t>Verify sort by departure time</t>
-  </si>
-  <si>
-    <t>1. Validate sort lists earliest departing train first.
-2. Validate departure time on each card matches sort order.
-3. Validate trains with same departure time maintain consistent ordering.</t>
-  </si>
-  <si>
-    <t>TS_Train_Sort_004</t>
-  </si>
-  <si>
-    <t>REQ_Train_Sort_004</t>
-  </si>
-  <si>
-    <t>Verify sort by arrival time</t>
-  </si>
-  <si>
-    <t>1. Validate sort lists earliest arriving train first.
-2. Validate arrival time on each card matches sort order.
-3. Validate overnight trains (next-day arrival) are ordered last.</t>
-  </si>
-  <si>
-    <t>TC ID</t>
   </si>
   <si>
     <t>Pre-Conditions</t>
@@ -400,6 +103,9 @@
   </si>
   <si>
     <t>TC_Train_001</t>
+  </si>
+  <si>
+    <t>TS_Train_Search_001</t>
   </si>
   <si>
     <t>1. User has a valid account registered on redBus
@@ -541,18 +247,6 @@
     <t>To validate that the source and destination input fields can be cleared</t>
   </si>
   <si>
-    <t>1. Open browser and go to www.redbus.in
-2. Click 'Account' icon → 'Login'
-3. Enter mobile: 9876543210 → Enter OTP → Continue
-4. Navigate to www.redbus.in/railways
-5. Enter 'Howrah Jn (HWH)' in From field
-6. Enter 'New Delhi (NDLS)' in To field
-7. Click the clear/cross (✕) icon on the From field
-8. Observe if From field is cleared
-9. Click the clear/cross (✕) icon on the To field
-10. Observe if To field is cleared</t>
-  </si>
-  <si>
     <t>From: Howrah Jn (HWH) | To: New Delhi (NDLS)</t>
   </si>
   <si>
@@ -566,6 +260,9 @@
   </si>
   <si>
     <t>TC_Train_006</t>
+  </si>
+  <si>
+    <t>TS_Train_Search_002</t>
   </si>
   <si>
     <t>To validate error is shown when source and destination are same</t>
@@ -649,6 +346,9 @@
     <t>TC_Train_009</t>
   </si>
   <si>
+    <t>TS_Train_Search_003</t>
+  </si>
+  <si>
     <t>1. User has a valid account registered on redBus/redRail
 2. Browser is open
 3. User is NOT logged in</t>
@@ -785,6 +485,9 @@
     <t>TC_Train_014</t>
   </si>
   <si>
+    <t>TS_Train_Search_004</t>
+  </si>
+  <si>
     <t>To validate Free Cancellation toggle is visible and OFF by default</t>
   </si>
   <si>
@@ -867,6 +570,9 @@
     <t>TC_Train_017</t>
   </si>
   <si>
+    <t>TS_Train_Filter_001</t>
+  </si>
+  <si>
     <t>To validate all class filter options are listed</t>
   </si>
   <si>
@@ -967,6 +673,9 @@
     <t>TC_Train_021</t>
   </si>
   <si>
+    <t>TS_Train_Filter_002</t>
+  </si>
+  <si>
     <t>To validate General quota filter shows correct availability</t>
   </si>
   <si>
@@ -1042,6 +751,9 @@
     <t>TC_Train_024</t>
   </si>
   <si>
+    <t>TS_Train_Filter_003</t>
+  </si>
+  <si>
     <t>To validate AC filter shows only AC trains</t>
   </si>
   <si>
@@ -1088,6 +800,9 @@
   </si>
   <si>
     <t>TC_Train_026</t>
+  </si>
+  <si>
+    <t>TS_Train_Filter_004</t>
   </si>
   <si>
     <t>To validate Clear All removes all applied filters</t>
@@ -1117,6 +832,9 @@
     <t>TC_Train_027</t>
   </si>
   <si>
+    <t>TS_Train_Sort_001</t>
+  </si>
+  <si>
     <t>To validate sort by arrival time descending works correctly</t>
   </si>
   <si>
@@ -1165,6 +883,9 @@
     <t>TC_Train_029</t>
   </si>
   <si>
+    <t>TS_Train_Sort_002</t>
+  </si>
+  <si>
     <t>To validate sort by duration ascending works correctly</t>
   </si>
   <si>
@@ -1213,6 +934,9 @@
     <t>TC_Train_031</t>
   </si>
   <si>
+    <t>TS_Train_Sort_003</t>
+  </si>
+  <si>
     <t>To validate sort by departure time asending works correctly</t>
   </si>
   <si>
@@ -1235,6 +959,9 @@
   </si>
   <si>
     <t>TC_Train_032</t>
+  </si>
+  <si>
+    <t>TS_Train_Sort_004</t>
   </si>
   <si>
     <t>To validate sort by departure time  descending works correctly</t>
@@ -1259,6 +986,263 @@
     <t>Trains shown with descending departure time</t>
   </si>
   <si>
+    <t>Issue Type</t>
+  </si>
+  <si>
+    <t>Summary</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>Epic</t>
+  </si>
+  <si>
+    <t>Bus Search and Filter Functionality</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Story</t>
+  </si>
+  <si>
+    <t>User searches trains between stations</t>
+  </si>
+  <si>
+    <t>Sub-story</t>
+  </si>
+  <si>
+    <t>Enter source and destination station</t>
+  </si>
+  <si>
+    <t>Validate same source and destination</t>
+  </si>
+  <si>
+    <t>Select journey date</t>
+  </si>
+  <si>
+    <t>Enable free cancellation filter in search</t>
+  </si>
+  <si>
+    <t>User applies filters to bus results</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Filter by class (Sleeper, AC 3-tier, AC 2-tier, etc.)</t>
+  </si>
+  <si>
+    <t>Filter by quota (General, Ladies, Tatkal)</t>
+  </si>
+  <si>
+    <t>Filter by AC / Non-AC</t>
+  </si>
+  <si>
+    <t>Clear all applied filters</t>
+  </si>
+  <si>
+    <t>User sorts bus search results</t>
+  </si>
+  <si>
+    <t>Sort by price (low to high / high to low)</t>
+  </si>
+  <si>
+    <t>Sort by duration</t>
+  </si>
+  <si>
+    <t>Sort by departure time</t>
+  </si>
+  <si>
+    <t>Sort by arrival time</t>
+  </si>
+  <si>
+    <t>Module 3: Bus Search &amp; Filter</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Total Epics</t>
+  </si>
+  <si>
+    <t>Total Stories</t>
+  </si>
+  <si>
+    <t>Total Sub-stories</t>
+  </si>
+  <si>
+    <t>High Priority Items</t>
+  </si>
+  <si>
+    <t>Medium Priority Items</t>
+  </si>
+  <si>
+    <t>Low Priority Items</t>
+  </si>
+  <si>
+    <t>Requirement ID</t>
+  </si>
+  <si>
+    <t>Test Scenario Description</t>
+  </si>
+  <si>
+    <t>Type of Testing</t>
+  </si>
+  <si>
+    <t>Possible No. of Test Cases</t>
+  </si>
+  <si>
+    <t>Test Case Details</t>
+  </si>
+  <si>
+    <t>REQ_Train_Search_001</t>
+  </si>
+  <si>
+    <t>Verify source and destination station entry</t>
+  </si>
+  <si>
+    <t>Functional Testing</t>
+  </si>
+  <si>
+    <t>1. To validate both source and destination left blank
+2. To validate search results load when both source and destination are correctly filled
+3. To validate source and destination filled using autocomplete and search results load
+4. To validate behaviour when source is valid and destination is invalid/wrong</t>
+  </si>
+  <si>
+    <t>REQ_Train_Search_002</t>
+  </si>
+  <si>
+    <t>Verify validation when source and destination are the same</t>
+  </si>
+  <si>
+    <t>1. Validate error shown when source equals destination.
+2. Validate Search button is blocked on same-station entry.
+3. Validate error clears when destination is changed.</t>
+  </si>
+  <si>
+    <t>REQ_Train_Search_003</t>
+  </si>
+  <si>
+    <t>Verify journey date selection behaviour</t>
+  </si>
+  <si>
+    <t>1. Validate date picker opens on clicking date field.
+2. Validate past dates are disabled and cannot be selected.
+3. Validate today's date is selectable.
+4. Validate tomorrow's date can be selected.
+5. Validate selected date is displayed correctly in the field.</t>
+  </si>
+  <si>
+    <t>REQ_Train_Search_004</t>
+  </si>
+  <si>
+    <t>Verify free cancellation toggle in search</t>
+  </si>
+  <si>
+    <t>1. Validate free cancellation toggle is visible on search screen.
+2. Validate clicking toggle enables the filter (turns ON).
+3. Validate results show only free-cancellation trains when ON.
+4. Validate disabling toggle restores the full results.</t>
+  </si>
+  <si>
+    <t>REQ_Train_Filter_001</t>
+  </si>
+  <si>
+    <t>Verify filter by train class (Sleeper, AC 3-tier, AC 2-tier, etc.)</t>
+  </si>
+  <si>
+    <t>1. Validate all class options are listed (Sleeper, AC 3-tier, AC 2-tier, 1st AC).
+2. Validate selecting a single class filters results to that class only.
+3. Validate multi-class selection shows combined results.
+4. Validate deselecting a class removes it from filter.
+5. Validate no-results message when no trains match.</t>
+  </si>
+  <si>
+    <t>REQ_Train_Filter_002</t>
+  </si>
+  <si>
+    <t>Verify filter by quota (General, Ladies, Tatkal)</t>
+  </si>
+  <si>
+    <t>1. Validate General, Ladies, Tatkal quota options are available.
+2. Validate General quota shows correct availability.
+3. Validate Tatkal quota reflects Tatkal pricing.
+4. Validate Ladies quota shows berths with ladies quota.</t>
+  </si>
+  <si>
+    <t>REQ_Train_Filter_003</t>
+  </si>
+  <si>
+    <t>Verify AC / Non-AC top filter</t>
+  </si>
+  <si>
+    <t>1. Validate AC filter shows only AC class trains (1A, 2A, 3A, CC).
+2. Validate Non-AC filter shows only non-AC trains (Sleeper, 2S).
+3. Validate selecting both returns all available trains.</t>
+  </si>
+  <si>
+    <t>REQ_Train_Filter_004</t>
+  </si>
+  <si>
+    <t>Verify clear all filters functionality</t>
+  </si>
+  <si>
+    <t>1. Validate 'Clear All' button is visible when filters are applied.
+2. Validate clicking 'Clear All' removes all active filters at once.
+3. Validate results revert to full unfiltered list after clearing.</t>
+  </si>
+  <si>
+    <t>REQ_Train_Sort_001</t>
+  </si>
+  <si>
+    <t>Verify sort by price (low to high / high to low)</t>
+  </si>
+  <si>
+    <t>1. Validate 'Sort by Price' option is available in the sort menu.
+2. Validate 'Low to High' lists cheapest fare train first.
+3. Validate 'High to Low' lists most expensive fare train first.
+4. Validate sort updates the list immediately.</t>
+  </si>
+  <si>
+    <t>REQ_Train_Sort_002</t>
+  </si>
+  <si>
+    <t>Verify sort by journey duration</t>
+  </si>
+  <si>
+    <t>1. Validate ascending sort lists shortest journey train first.
+2. Validate descending sort lists longest journey train first.
+3. Validate trains with equal duration maintain consistent order.</t>
+  </si>
+  <si>
+    <t>REQ_Train_Sort_003</t>
+  </si>
+  <si>
+    <t>Verify sort by departure time</t>
+  </si>
+  <si>
+    <t>1. Validate sort lists earliest departing train first.
+2. Validate departure time on each card matches sort order.
+3. Validate trains with same departure time maintain consistent ordering.</t>
+  </si>
+  <si>
+    <t>REQ_Train_Sort_004</t>
+  </si>
+  <si>
+    <t>Verify sort by arrival time</t>
+  </si>
+  <si>
+    <t>1. Validate sort lists earliest arriving train first.
+2. Validate arrival time on each card matches sort order.
+3. Validate overnight trains (next-day arrival) are ordered last.</t>
+  </si>
+  <si>
     <t>BR_ID</t>
   </si>
   <si>
@@ -1328,17 +1312,115 @@
     <t>The From and To station input fields can not be cleared the entered station name; previously entered station remains in the field after clearing</t>
   </si>
   <si>
-    <t>abc@capgemini.com</t>
-  </si>
-  <si>
     <t>To do</t>
+  </si>
+  <si>
+    <t>TEST EXECUTION SUMMARY</t>
+  </si>
+  <si>
+    <t>Project Name</t>
+  </si>
+  <si>
+    <t>Module Name</t>
+  </si>
+  <si>
+    <t>Total Cases</t>
+  </si>
+  <si>
+    <t>Total Passed</t>
+  </si>
+  <si>
+    <t>Total Failed</t>
+  </si>
+  <si>
+    <t>Total Executed</t>
+  </si>
+  <si>
+    <t>Pass Percentage</t>
+  </si>
+  <si>
+    <t>Fail Percentage</t>
+  </si>
+  <si>
+    <t>Completion Percentage</t>
+  </si>
+  <si>
+    <t>Verify Source and Destination Station Entry</t>
+  </si>
+  <si>
+    <t>80%</t>
+  </si>
+  <si>
+    <t>20%</t>
+  </si>
+  <si>
+    <t>100%</t>
+  </si>
+  <si>
+    <t>Verify Validation When Source and Destination Are the Same</t>
+  </si>
+  <si>
+    <t>0%</t>
+  </si>
+  <si>
+    <t>Verify Journey Date Selection Behaviour</t>
+  </si>
+  <si>
+    <t>Verify Free Cancellation Toggle in Search</t>
+  </si>
+  <si>
+    <t>Verify Filter by Train Class (Sleeper, AC 3-tier, AC 2-tier, etc.)</t>
+  </si>
+  <si>
+    <t>Verify Filter by Quota (General, Ladies, Tatkal)</t>
+  </si>
+  <si>
+    <t>Verify AC / Non-AC Top Filter</t>
+  </si>
+  <si>
+    <t>Verify Clear All Filters Functionality</t>
+  </si>
+  <si>
+    <t>Verify Sort by Price (Low to High / High to Low)</t>
+  </si>
+  <si>
+    <t>Verify Sort by Journey Duration</t>
+  </si>
+  <si>
+    <t>Verify Sort by Departure Time</t>
+  </si>
+  <si>
+    <t>Verify Sort by Arrival Time</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>97%</t>
+  </si>
+  <si>
+    <t>3%</t>
+  </si>
+  <si>
+    <t>abc@sdc</t>
+  </si>
+  <si>
+    <t>1. Open browser and go to www.redbus.in
+2. Click 'Account' icon → 'Login'
+3. Enter mobile: 9876543210 → Enter OTP → Continue
+4. Navigate to www.redbus.in/railways
+5. Enter 'Howrah Jn (HWH)' in From field
+6. Enter 'New Delhi (NDLS)' in To field
+7. Clear the From field
+8. Observe if From field is cleared
+9. Observe if To field is cleared</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="34" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1516,8 +1598,68 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF375623"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF92D050"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="19">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1622,12 +1764,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor rgb="FFF0F5FB"/>
+        <fgColor rgb="FF1F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6E4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -1693,18 +1844,63 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFAAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFAAAAAA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1862,11 +2058,70 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2139,167 +2394,167 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
+      <c r="A1" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>5</v>
+      <c r="A2" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>5</v>
+      <c r="A3" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="8"/>
+      <c r="A4" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="C4" s="6"/>
     </row>
     <row r="5" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="8"/>
+      <c r="A5" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="C5" s="6"/>
     </row>
     <row r="6" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="8"/>
+      <c r="A6" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="C6" s="6"/>
     </row>
     <row r="7" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="8"/>
+      <c r="A7" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="C7" s="6"/>
     </row>
     <row r="8" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>14</v>
+      <c r="A8" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="8"/>
+      <c r="A9" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="C9" s="6"/>
     </row>
     <row r="10" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="8"/>
+      <c r="A10" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="C10" s="6"/>
     </row>
     <row r="11" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="8"/>
+      <c r="A11" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="C11" s="6"/>
     </row>
     <row r="12" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="8"/>
+      <c r="A12" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="C12" s="6"/>
     </row>
     <row r="13" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>14</v>
+      <c r="A13" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="8"/>
+      <c r="A14" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="C14" s="6"/>
     </row>
     <row r="15" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="8"/>
+      <c r="A15" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="C15" s="6"/>
     </row>
     <row r="16" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="8"/>
+      <c r="A16" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="C16" s="6"/>
     </row>
     <row r="17" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" s="8"/>
+      <c r="A17" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="C17" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:C1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -2318,64 +2573,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1" s="1"/>
+      <c r="A1" s="69" t="s">
+        <v>256</v>
+      </c>
+      <c r="B1" s="70"/>
     </row>
     <row r="2" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>26</v>
+      <c r="A2" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" s="14">
+      <c r="A3" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="B3" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="16">
+      <c r="A4" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="B4" s="14">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="14">
+      <c r="A5" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="B5" s="12">
         <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" s="16">
+      <c r="A6" s="13" t="s">
+        <v>262</v>
+      </c>
+      <c r="B6" s="14">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="14">
+      <c r="A7" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="B7" s="12">
         <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="16">
+      <c r="A8" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="B8" s="14">
         <v>1</v>
       </c>
     </row>
@@ -2402,263 +2657,263 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>38</v>
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="84.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="B2" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="C2" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="E2" s="21">
+      <c r="A2" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>270</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>271</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>272</v>
+      </c>
+      <c r="E2" s="19">
         <v>4</v>
       </c>
-      <c r="F2" s="19" t="s">
-        <v>43</v>
+      <c r="F2" s="17" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="84.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="B3" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="C3" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="E3" s="25">
+      <c r="A3" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>274</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>275</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>272</v>
+      </c>
+      <c r="E3" s="23">
         <v>3</v>
       </c>
-      <c r="F3" s="24" t="s">
-        <v>47</v>
+      <c r="F3" s="22" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="84.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="E4" s="21">
+      <c r="A4" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>277</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>278</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>272</v>
+      </c>
+      <c r="E4" s="19">
         <v>5</v>
       </c>
-      <c r="F4" s="19" t="s">
-        <v>51</v>
+      <c r="F4" s="17" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="84.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="B5" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="C5" s="24" t="s">
-        <v>54</v>
-      </c>
-      <c r="D5" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="E5" s="25">
+      <c r="A5" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>280</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>272</v>
+      </c>
+      <c r="E5" s="23">
         <v>4</v>
       </c>
-      <c r="F5" s="24" t="s">
-        <v>55</v>
+      <c r="F5" s="22" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="84.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="E6" s="21">
+      <c r="A6" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>283</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>284</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>272</v>
+      </c>
+      <c r="E6" s="19">
         <v>5</v>
       </c>
-      <c r="F6" s="19" t="s">
-        <v>59</v>
+      <c r="F6" s="17" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="84.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="B7" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="D7" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="E7" s="25">
+      <c r="A7" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>286</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>287</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>272</v>
+      </c>
+      <c r="E7" s="23">
         <v>4</v>
       </c>
-      <c r="F7" s="24" t="s">
-        <v>63</v>
+      <c r="F7" s="22" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="84.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="E8" s="21">
+      <c r="A8" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>289</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>290</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>272</v>
+      </c>
+      <c r="E8" s="19">
         <v>3</v>
       </c>
-      <c r="F8" s="19" t="s">
-        <v>67</v>
+      <c r="F8" s="17" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="84.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="B9" s="23" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="E9" s="25">
+      <c r="A9" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>292</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>293</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>272</v>
+      </c>
+      <c r="E9" s="23">
         <v>3</v>
       </c>
-      <c r="F9" s="24" t="s">
-        <v>71</v>
+      <c r="F9" s="22" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="84.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="E10" s="21">
+      <c r="A10" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>296</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>272</v>
+      </c>
+      <c r="E10" s="19">
         <v>4</v>
       </c>
-      <c r="F10" s="19" t="s">
-        <v>75</v>
+      <c r="F10" s="17" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="84.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="22" t="s">
-        <v>76</v>
-      </c>
-      <c r="B11" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="C11" s="24" t="s">
-        <v>78</v>
-      </c>
-      <c r="D11" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="E11" s="25">
+      <c r="A11" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>298</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>299</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>272</v>
+      </c>
+      <c r="E11" s="23">
         <v>3</v>
       </c>
-      <c r="F11" s="24" t="s">
-        <v>79</v>
+      <c r="F11" s="22" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="84.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="E12" s="21">
+      <c r="A12" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>301</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>302</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>272</v>
+      </c>
+      <c r="E12" s="19">
         <v>3</v>
       </c>
-      <c r="F12" s="19" t="s">
-        <v>83</v>
+      <c r="F12" s="17" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="84.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="22" t="s">
-        <v>84</v>
-      </c>
-      <c r="B13" s="23" t="s">
-        <v>85</v>
-      </c>
-      <c r="C13" s="24" t="s">
-        <v>86</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="E13" s="25">
+      <c r="A13" s="20" t="s">
+        <v>226</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>304</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>305</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>272</v>
+      </c>
+      <c r="E13" s="23">
         <v>3</v>
       </c>
-      <c r="F13" s="24" t="s">
-        <v>87</v>
+      <c r="F13" s="22" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="84.75" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -2691,1214 +2946,1214 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="67" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="68"/>
+      <c r="J1" s="67" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="68"/>
+      <c r="L1" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="M1" s="25" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" s="27" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" s="30"/>
+      <c r="K3" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" s="33"/>
+      <c r="M3" s="34"/>
+    </row>
+    <row r="4" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" s="37"/>
+      <c r="K4" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="L4" s="38"/>
+      <c r="M4" s="39"/>
+    </row>
+    <row r="5" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="I5" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5" s="30"/>
+      <c r="K5" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="L5" s="33"/>
+      <c r="M5" s="34"/>
+    </row>
+    <row r="6" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="H6" s="37" t="s">
+        <v>48</v>
+      </c>
+      <c r="I6" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="J6" s="37"/>
+      <c r="K6" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="L6" s="38"/>
+      <c r="M6" s="39"/>
+    </row>
+    <row r="7" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>361</v>
+      </c>
+      <c r="F7" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="H7" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="I7" s="40" t="s">
+        <v>55</v>
+      </c>
+      <c r="J7" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="K7" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="L7" s="41" t="s">
+        <v>54</v>
+      </c>
+      <c r="M7" s="34"/>
+    </row>
+    <row r="8" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="F8" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="G8" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="H8" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="I8" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="J8" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="K8" s="42" t="s">
+        <v>63</v>
+      </c>
+      <c r="L8" s="38"/>
+      <c r="M8" s="39"/>
+    </row>
+    <row r="9" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="F9" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="G9" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="H9" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="I9" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="J9" s="37"/>
+      <c r="K9" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="L9" s="33"/>
+      <c r="M9" s="34"/>
+    </row>
+    <row r="10" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="F10" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="G10" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="H10" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="I10" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="J10" s="30"/>
+      <c r="K10" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="L10" s="38"/>
+      <c r="M10" s="39"/>
+    </row>
+    <row r="11" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="35" t="s">
+        <v>76</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="F11" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="G11" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="H11" s="37" t="s">
+        <v>83</v>
+      </c>
+      <c r="I11" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="J11" s="37"/>
+      <c r="K11" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="L11" s="33"/>
+      <c r="M11" s="34"/>
+    </row>
+    <row r="12" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="F12" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="G12" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="C1" s="26" t="s">
+      <c r="H12" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="I12" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="J12" s="30"/>
+      <c r="K12" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="L12" s="38"/>
+      <c r="M12" s="39"/>
+    </row>
+    <row r="13" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="35" t="s">
         <v>90</v>
       </c>
-      <c r="E1" s="26" t="s">
+      <c r="B13" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="D13" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="E13" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="G1" s="26" t="s">
+      <c r="F13" s="37" t="s">
         <v>93</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="G13" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2" t="s">
+      <c r="H13" s="37" t="s">
         <v>95</v>
       </c>
-      <c r="K1" s="2"/>
-      <c r="L1" s="27" t="s">
+      <c r="I13" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="J13" s="37"/>
+      <c r="K13" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="L13" s="33"/>
+      <c r="M13" s="34"/>
+    </row>
+    <row r="14" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="28" t="s">
         <v>96</v>
       </c>
-      <c r="M1" s="27" t="s">
+      <c r="B14" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" s="22" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="28" t="s">
-        <v>88</v>
-      </c>
-      <c r="B2" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="C2" s="28" t="s">
+      <c r="E14" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="D2" s="28" t="s">
+      <c r="F14" s="30" t="s">
         <v>99</v>
       </c>
-      <c r="E2" s="28" t="s">
+      <c r="G14" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="F2" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="G2" s="28" t="s">
-        <v>93</v>
-      </c>
-      <c r="H2" s="28" t="s">
+      <c r="H14" s="30" t="s">
         <v>101</v>
       </c>
-      <c r="I2" s="28" t="s">
+      <c r="I14" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="J14" s="30"/>
+      <c r="K14" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="L14" s="38"/>
+      <c r="M14" s="39"/>
+    </row>
+    <row r="15" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="35" t="s">
         <v>102</v>
       </c>
-      <c r="J2" s="28" t="s">
+      <c r="B15" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="K2" s="28" t="s">
+      <c r="E15" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="L2" s="29" t="s">
+      <c r="F15" s="37" t="s">
         <v>105</v>
       </c>
-      <c r="M2" s="29" t="s">
+      <c r="G15" s="17" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="30" t="s">
+      <c r="H15" s="37" t="s">
         <v>107</v>
       </c>
-      <c r="B3" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="C3" s="24" t="s">
+      <c r="I15" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="J15" s="37"/>
+      <c r="K15" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="L15" s="33"/>
+      <c r="M15" s="34"/>
+    </row>
+    <row r="16" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="24" t="s">
+      <c r="B16" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="E3" s="24" t="s">
+      <c r="C16" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="F3" s="31" t="s">
+      <c r="E16" s="22" t="s">
         <v>111</v>
       </c>
-      <c r="G3" s="24" t="s">
+      <c r="F16" s="30" t="s">
         <v>112</v>
       </c>
-      <c r="H3" s="32" t="s">
-        <v>112</v>
-      </c>
-      <c r="I3" s="33" t="s">
+      <c r="G16" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="J3" s="32"/>
-      <c r="K3" s="34" t="s">
+      <c r="H16" s="30" t="s">
         <v>114</v>
       </c>
-      <c r="L3" s="35"/>
-      <c r="M3" s="36"/>
-    </row>
-    <row r="4" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="37" t="s">
+      <c r="I16" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="J16" s="30"/>
+      <c r="K16" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="L16" s="38"/>
+      <c r="M16" s="39"/>
+    </row>
+    <row r="17" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="35" t="s">
         <v>115</v>
       </c>
-      <c r="B4" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4" s="19" t="s">
+      <c r="B17" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="E17" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="F17" s="37" t="s">
         <v>118</v>
       </c>
-      <c r="F4" s="38" t="s">
+      <c r="G17" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="G4" s="19" t="s">
+      <c r="H17" s="37" t="s">
         <v>120</v>
       </c>
-      <c r="H4" s="39" t="s">
+      <c r="I17" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="J17" s="37"/>
+      <c r="K17" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="L17" s="33"/>
+      <c r="M17" s="34"/>
+    </row>
+    <row r="18" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="I4" s="33" t="s">
-        <v>113</v>
-      </c>
-      <c r="J4" s="39"/>
-      <c r="K4" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="L4" s="40"/>
-      <c r="M4" s="41"/>
-    </row>
-    <row r="5" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="30" t="s">
+      <c r="B18" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="C18" s="22" t="s">
         <v>122</v>
       </c>
-      <c r="B5" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="D5" s="24" t="s">
+      <c r="D18" s="22" t="s">
         <v>123</v>
       </c>
-      <c r="E5" s="24" t="s">
+      <c r="E18" s="22" t="s">
         <v>124</v>
       </c>
-      <c r="F5" s="31" t="s">
+      <c r="F18" s="30" t="s">
         <v>125</v>
       </c>
-      <c r="G5" s="24" t="s">
+      <c r="G18" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="H5" s="32" t="s">
+      <c r="H18" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="I5" s="33" t="s">
-        <v>113</v>
-      </c>
-      <c r="J5" s="32"/>
-      <c r="K5" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="L5" s="35"/>
-      <c r="M5" s="36"/>
-    </row>
-    <row r="6" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="37" t="s">
+      <c r="I18" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="J18" s="30"/>
+      <c r="K18" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="L18" s="38"/>
+      <c r="M18" s="39"/>
+    </row>
+    <row r="19" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="35" t="s">
         <v>128</v>
       </c>
-      <c r="B6" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="C6" s="19" t="s">
+      <c r="B19" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="C19" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E19" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="F6" s="38" t="s">
+      <c r="F19" s="37" t="s">
         <v>132</v>
       </c>
-      <c r="G6" s="19" t="s">
+      <c r="G19" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="H6" s="39" t="s">
+      <c r="H19" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="I6" s="33" t="s">
-        <v>113</v>
-      </c>
-      <c r="J6" s="39"/>
-      <c r="K6" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="L6" s="40"/>
-      <c r="M6" s="41"/>
-    </row>
-    <row r="7" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="37" t="s">
+      <c r="I19" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="J19" s="37"/>
+      <c r="K19" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="L19" s="33"/>
+      <c r="M19" s="34"/>
+    </row>
+    <row r="20" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="28" t="s">
         <v>135</v>
       </c>
-      <c r="B7" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="C7" s="19" t="s">
+      <c r="B20" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="D20" s="22" t="s">
         <v>136</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="E20" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="F20" s="30" t="s">
         <v>138</v>
       </c>
-      <c r="F7" s="38" t="s">
+      <c r="G20" s="22" t="s">
         <v>139</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="H20" s="30" t="s">
         <v>140</v>
       </c>
-      <c r="H7" s="39" t="s">
+      <c r="I20" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="J20" s="30"/>
+      <c r="K20" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="L20" s="38"/>
+      <c r="M20" s="39"/>
+    </row>
+    <row r="21" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="35" t="s">
         <v>141</v>
       </c>
-      <c r="I7" s="42" t="s">
+      <c r="B21" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="D21" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="J7" s="39" t="s">
-        <v>141</v>
-      </c>
-      <c r="K7" s="56" t="s">
-        <v>142</v>
-      </c>
-      <c r="L7" s="43" t="s">
-        <v>141</v>
-      </c>
-      <c r="M7" s="36"/>
-    </row>
-    <row r="8" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="30" t="s">
+      <c r="E21" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="B8" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" s="24" t="s">
+      <c r="F21" s="37" t="s">
+        <v>144</v>
+      </c>
+      <c r="G21" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="H21" s="37" t="s">
+        <v>146</v>
+      </c>
+      <c r="I21" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="J21" s="37"/>
+      <c r="K21" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="L21" s="33"/>
+      <c r="M21" s="34"/>
+    </row>
+    <row r="22" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="B22" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="D8" s="24" t="s">
-        <v>144</v>
-      </c>
-      <c r="E8" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="F8" s="32" t="s">
-        <v>146</v>
-      </c>
-      <c r="G8" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="H8" s="32" t="s">
+      <c r="C22" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="D22" s="22" t="s">
         <v>148</v>
       </c>
-      <c r="I8" s="33" t="s">
-        <v>113</v>
-      </c>
-      <c r="J8" s="32" t="s">
+      <c r="E22" s="22" t="s">
         <v>149</v>
       </c>
-      <c r="K8" s="44" t="s">
-        <v>149</v>
-      </c>
-      <c r="L8" s="40"/>
-      <c r="M8" s="41"/>
-    </row>
-    <row r="9" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="37" t="s">
+      <c r="F22" s="30" t="s">
         <v>150</v>
       </c>
-      <c r="B9" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="D9" s="19" t="s">
+      <c r="G22" s="22" t="s">
         <v>151</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="H22" s="30" t="s">
         <v>152</v>
       </c>
-      <c r="F9" s="39" t="s">
+      <c r="I22" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="J22" s="30"/>
+      <c r="K22" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="L22" s="38"/>
+      <c r="M22" s="39"/>
+    </row>
+    <row r="23" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="35" t="s">
         <v>153</v>
       </c>
-      <c r="G9" s="19" t="s">
+      <c r="B23" s="15" t="s">
         <v>154</v>
       </c>
-      <c r="H9" s="39" t="s">
+      <c r="C23" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="D23" s="17" t="s">
         <v>155</v>
       </c>
-      <c r="I9" s="33" t="s">
-        <v>113</v>
-      </c>
-      <c r="J9" s="39"/>
-      <c r="K9" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="L9" s="35"/>
-      <c r="M9" s="36"/>
-    </row>
-    <row r="10" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="30" t="s">
+      <c r="E23" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="B10" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>129</v>
-      </c>
-      <c r="D10" s="24" t="s">
+      <c r="F23" s="37" t="s">
         <v>157</v>
       </c>
-      <c r="E10" s="24" t="s">
+      <c r="G23" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="F10" s="32" t="s">
+      <c r="H23" s="37" t="s">
         <v>159</v>
       </c>
-      <c r="G10" s="24" t="s">
+      <c r="I23" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="J23" s="37"/>
+      <c r="K23" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="L23" s="33"/>
+      <c r="M23" s="34"/>
+    </row>
+    <row r="24" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="28" t="s">
         <v>160</v>
       </c>
-      <c r="H10" s="32" t="s">
+      <c r="B24" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="C24" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="D24" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="I10" s="33" t="s">
-        <v>113</v>
-      </c>
-      <c r="J10" s="32"/>
-      <c r="K10" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="L10" s="40"/>
-      <c r="M10" s="41"/>
-    </row>
-    <row r="11" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="37" t="s">
+      <c r="E24" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="B11" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="C11" s="19" t="s">
+      <c r="F24" s="30" t="s">
         <v>163</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="G24" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="H24" s="30" t="s">
         <v>165</v>
       </c>
-      <c r="F11" s="39" t="s">
+      <c r="I24" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="J24" s="30"/>
+      <c r="K24" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="L24" s="38"/>
+      <c r="M24" s="39"/>
+    </row>
+    <row r="25" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="35" t="s">
         <v>166</v>
       </c>
-      <c r="G11" s="19" t="s">
+      <c r="B25" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="D25" s="17" t="s">
         <v>167</v>
       </c>
-      <c r="H11" s="39" t="s">
+      <c r="E25" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="I11" s="33" t="s">
-        <v>113</v>
-      </c>
-      <c r="J11" s="39"/>
-      <c r="K11" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="L11" s="35"/>
-      <c r="M11" s="36"/>
-    </row>
-    <row r="12" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="30" t="s">
+      <c r="F25" s="37" t="s">
         <v>169</v>
       </c>
-      <c r="B12" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" s="24" t="s">
-        <v>163</v>
-      </c>
-      <c r="D12" s="24" t="s">
+      <c r="G25" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="E12" s="24" t="s">
+      <c r="H25" s="37" t="s">
         <v>171</v>
       </c>
-      <c r="F12" s="32" t="s">
+      <c r="I25" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="J25" s="37"/>
+      <c r="K25" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="L25" s="33"/>
+      <c r="M25" s="34"/>
+    </row>
+    <row r="26" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="28" t="s">
         <v>172</v>
       </c>
-      <c r="G12" s="24" t="s">
+      <c r="B26" s="20" t="s">
         <v>173</v>
       </c>
-      <c r="H12" s="32" t="s">
+      <c r="C26" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="D26" s="22" t="s">
         <v>174</v>
       </c>
-      <c r="I12" s="33" t="s">
-        <v>113</v>
-      </c>
-      <c r="J12" s="32"/>
-      <c r="K12" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="L12" s="40"/>
-      <c r="M12" s="41"/>
-    </row>
-    <row r="13" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="37" t="s">
+      <c r="E26" s="22" t="s">
         <v>175</v>
       </c>
-      <c r="B13" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>163</v>
-      </c>
-      <c r="D13" s="19" t="s">
+      <c r="F26" s="30" t="s">
         <v>176</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="G26" s="22" t="s">
         <v>177</v>
       </c>
-      <c r="F13" s="39" t="s">
+      <c r="H26" s="30" t="s">
         <v>178</v>
       </c>
-      <c r="G13" s="19" t="s">
+      <c r="I26" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="J26" s="30"/>
+      <c r="K26" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="L26" s="38"/>
+      <c r="M26" s="39"/>
+    </row>
+    <row r="27" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="35" t="s">
         <v>179</v>
       </c>
-      <c r="H13" s="39" t="s">
+      <c r="B27" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="D27" s="17" t="s">
         <v>180</v>
       </c>
-      <c r="I13" s="33" t="s">
-        <v>113</v>
-      </c>
-      <c r="J13" s="39"/>
-      <c r="K13" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="L13" s="35"/>
-      <c r="M13" s="36"/>
-    </row>
-    <row r="14" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="30" t="s">
+      <c r="E27" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="B14" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="C14" s="24" t="s">
-        <v>129</v>
-      </c>
-      <c r="D14" s="24" t="s">
+      <c r="F27" s="37" t="s">
         <v>182</v>
       </c>
-      <c r="E14" s="24" t="s">
+      <c r="G27" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="F14" s="32" t="s">
+      <c r="H27" s="37" t="s">
         <v>184</v>
       </c>
-      <c r="G14" s="24" t="s">
+      <c r="I27" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="J27" s="37"/>
+      <c r="K27" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="L27" s="33"/>
+      <c r="M27" s="34"/>
+    </row>
+    <row r="28" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="28" t="s">
         <v>185</v>
       </c>
-      <c r="H14" s="32" t="s">
+      <c r="B28" s="20" t="s">
         <v>186</v>
       </c>
-      <c r="I14" s="33" t="s">
-        <v>113</v>
-      </c>
-      <c r="J14" s="32"/>
-      <c r="K14" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="L14" s="40"/>
-      <c r="M14" s="41"/>
-    </row>
-    <row r="15" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="37" t="s">
+      <c r="C28" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D28" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="B15" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="D15" s="19" t="s">
+      <c r="E28" s="22" t="s">
         <v>188</v>
       </c>
-      <c r="E15" s="19" t="s">
+      <c r="F28" s="30" t="s">
         <v>189</v>
       </c>
-      <c r="F15" s="39" t="s">
+      <c r="G28" s="22" t="s">
         <v>190</v>
       </c>
-      <c r="G15" s="19" t="s">
+      <c r="H28" s="30" t="s">
         <v>191</v>
       </c>
-      <c r="H15" s="39" t="s">
+      <c r="I28" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="J28" s="30"/>
+      <c r="K28" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="L28" s="38"/>
+      <c r="M28" s="39"/>
+    </row>
+    <row r="29" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="35" t="s">
         <v>192</v>
       </c>
-      <c r="I15" s="33" t="s">
-        <v>113</v>
-      </c>
-      <c r="J15" s="39"/>
-      <c r="K15" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="L15" s="35"/>
-      <c r="M15" s="36"/>
-    </row>
-    <row r="16" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="30" t="s">
+      <c r="B29" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="B16" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="C16" s="24" t="s">
-        <v>129</v>
-      </c>
-      <c r="D16" s="24" t="s">
+      <c r="C29" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="D29" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="E16" s="24" t="s">
+      <c r="E29" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="F16" s="32" t="s">
+      <c r="F29" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="G16" s="24" t="s">
+      <c r="G29" s="17" t="s">
         <v>197</v>
       </c>
-      <c r="H16" s="32" t="s">
+      <c r="H29" s="37" t="s">
         <v>198</v>
       </c>
-      <c r="I16" s="33" t="s">
-        <v>113</v>
-      </c>
-      <c r="J16" s="32"/>
-      <c r="K16" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="L16" s="40"/>
-      <c r="M16" s="41"/>
-    </row>
-    <row r="17" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="37" t="s">
+      <c r="I29" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="J29" s="37"/>
+      <c r="K29" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="L29" s="33"/>
+      <c r="M29" s="34"/>
+    </row>
+    <row r="30" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="28" t="s">
         <v>199</v>
       </c>
-      <c r="B17" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="D17" s="19" t="s">
+      <c r="B30" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="C30" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="D30" s="22" t="s">
         <v>200</v>
       </c>
-      <c r="E17" s="19" t="s">
+      <c r="E30" s="22" t="s">
         <v>201</v>
       </c>
-      <c r="F17" s="39" t="s">
+      <c r="F30" s="30" t="s">
         <v>202</v>
       </c>
-      <c r="G17" s="19" t="s">
+      <c r="G30" s="22" t="s">
         <v>203</v>
       </c>
-      <c r="H17" s="39" t="s">
+      <c r="H30" s="30" t="s">
         <v>204</v>
       </c>
-      <c r="I17" s="33" t="s">
-        <v>113</v>
-      </c>
-      <c r="J17" s="39"/>
-      <c r="K17" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="L17" s="35"/>
-      <c r="M17" s="36"/>
-    </row>
-    <row r="18" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="30" t="s">
+      <c r="I30" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="J30" s="30"/>
+      <c r="K30" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="L30" s="38"/>
+      <c r="M30" s="39"/>
+    </row>
+    <row r="31" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="B18" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="C18" s="24" t="s">
+      <c r="B31" s="15" t="s">
         <v>206</v>
       </c>
-      <c r="D18" s="24" t="s">
+      <c r="C31" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="D31" s="17" t="s">
         <v>207</v>
       </c>
-      <c r="E18" s="24" t="s">
+      <c r="E31" s="17" t="s">
         <v>208</v>
       </c>
-      <c r="F18" s="32" t="s">
+      <c r="F31" s="37" t="s">
         <v>209</v>
       </c>
-      <c r="G18" s="24" t="s">
+      <c r="G31" s="17" t="s">
         <v>210</v>
       </c>
-      <c r="H18" s="32" t="s">
+      <c r="H31" s="37" t="s">
         <v>211</v>
       </c>
-      <c r="I18" s="33" t="s">
-        <v>113</v>
-      </c>
-      <c r="J18" s="32"/>
-      <c r="K18" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="L18" s="40"/>
-      <c r="M18" s="41"/>
-    </row>
-    <row r="19" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="37" t="s">
+      <c r="I31" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="J31" s="37"/>
+      <c r="K31" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="L31" s="33"/>
+      <c r="M31" s="34"/>
+    </row>
+    <row r="32" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="28" t="s">
         <v>212</v>
       </c>
-      <c r="B19" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="D19" s="19" t="s">
+      <c r="B32" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="C32" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="D32" s="22" t="s">
         <v>213</v>
       </c>
-      <c r="E19" s="19" t="s">
+      <c r="E32" s="22" t="s">
         <v>214</v>
       </c>
-      <c r="F19" s="39" t="s">
+      <c r="F32" s="30" t="s">
         <v>215</v>
       </c>
-      <c r="G19" s="19" t="s">
+      <c r="G32" s="22" t="s">
         <v>216</v>
       </c>
-      <c r="H19" s="39" t="s">
+      <c r="H32" s="30" t="s">
         <v>217</v>
       </c>
-      <c r="I19" s="33" t="s">
-        <v>113</v>
-      </c>
-      <c r="J19" s="39"/>
-      <c r="K19" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="L19" s="35"/>
-      <c r="M19" s="36"/>
-    </row>
-    <row r="20" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="30" t="s">
+      <c r="I32" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="J32" s="30"/>
+      <c r="K32" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="L32" s="38"/>
+      <c r="M32" s="39"/>
+    </row>
+    <row r="33" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="35" t="s">
         <v>218</v>
       </c>
-      <c r="B20" s="22" t="s">
-        <v>56</v>
-      </c>
-      <c r="C20" s="24" t="s">
-        <v>206</v>
-      </c>
-      <c r="D20" s="24" t="s">
+      <c r="B33" s="15" t="s">
         <v>219</v>
       </c>
-      <c r="E20" s="24" t="s">
+      <c r="C33" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="D33" s="17" t="s">
         <v>220</v>
       </c>
-      <c r="F20" s="32" t="s">
+      <c r="E33" s="17" t="s">
         <v>221</v>
       </c>
-      <c r="G20" s="24" t="s">
+      <c r="F33" s="37" t="s">
         <v>222</v>
       </c>
-      <c r="H20" s="32" t="s">
+      <c r="G33" s="17" t="s">
         <v>223</v>
       </c>
-      <c r="I20" s="33" t="s">
-        <v>113</v>
-      </c>
-      <c r="J20" s="32"/>
-      <c r="K20" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="L20" s="40"/>
-      <c r="M20" s="41"/>
-    </row>
-    <row r="21" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="37" t="s">
+      <c r="H33" s="37" t="s">
         <v>224</v>
       </c>
-      <c r="B21" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="C21" s="19" t="s">
-        <v>206</v>
-      </c>
-      <c r="D21" s="19" t="s">
+      <c r="I33" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="J33" s="37"/>
+      <c r="K33" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="L33" s="33"/>
+      <c r="M33" s="34"/>
+    </row>
+    <row r="34" spans="1:13" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="28" t="s">
         <v>225</v>
       </c>
-      <c r="E21" s="19" t="s">
+      <c r="B34" s="20" t="s">
         <v>226</v>
       </c>
-      <c r="F21" s="39" t="s">
+      <c r="C34" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="D34" s="22" t="s">
         <v>227</v>
       </c>
-      <c r="G21" s="19" t="s">
+      <c r="E34" s="22" t="s">
         <v>228</v>
       </c>
-      <c r="H21" s="39" t="s">
+      <c r="F34" s="30" t="s">
         <v>229</v>
       </c>
-      <c r="I21" s="33" t="s">
-        <v>113</v>
-      </c>
-      <c r="J21" s="39"/>
-      <c r="K21" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="L21" s="35"/>
-      <c r="M21" s="36"/>
-    </row>
-    <row r="22" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="30" t="s">
+      <c r="G34" s="22" t="s">
         <v>230</v>
       </c>
-      <c r="B22" s="22" t="s">
-        <v>56</v>
-      </c>
-      <c r="C22" s="24" t="s">
-        <v>206</v>
-      </c>
-      <c r="D22" s="24" t="s">
+      <c r="H34" s="30" t="s">
         <v>231</v>
       </c>
-      <c r="E22" s="24" t="s">
-        <v>232</v>
-      </c>
-      <c r="F22" s="32" t="s">
-        <v>233</v>
-      </c>
-      <c r="G22" s="24" t="s">
-        <v>234</v>
-      </c>
-      <c r="H22" s="32" t="s">
-        <v>235</v>
-      </c>
-      <c r="I22" s="33" t="s">
-        <v>113</v>
-      </c>
-      <c r="J22" s="32"/>
-      <c r="K22" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="L22" s="40"/>
-      <c r="M22" s="41"/>
-    </row>
-    <row r="23" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="37" t="s">
-        <v>236</v>
-      </c>
-      <c r="B23" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="C23" s="19" t="s">
-        <v>206</v>
-      </c>
-      <c r="D23" s="19" t="s">
-        <v>237</v>
-      </c>
-      <c r="E23" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="F23" s="39" t="s">
-        <v>239</v>
-      </c>
-      <c r="G23" s="19" t="s">
-        <v>240</v>
-      </c>
-      <c r="H23" s="39" t="s">
-        <v>241</v>
-      </c>
-      <c r="I23" s="33" t="s">
-        <v>113</v>
-      </c>
-      <c r="J23" s="39"/>
-      <c r="K23" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="L23" s="35"/>
-      <c r="M23" s="36"/>
-    </row>
-    <row r="24" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="30" t="s">
-        <v>242</v>
-      </c>
-      <c r="B24" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="C24" s="24" t="s">
-        <v>206</v>
-      </c>
-      <c r="D24" s="24" t="s">
-        <v>243</v>
-      </c>
-      <c r="E24" s="24" t="s">
-        <v>244</v>
-      </c>
-      <c r="F24" s="32" t="s">
-        <v>245</v>
-      </c>
-      <c r="G24" s="24" t="s">
-        <v>246</v>
-      </c>
-      <c r="H24" s="32" t="s">
-        <v>247</v>
-      </c>
-      <c r="I24" s="33" t="s">
-        <v>113</v>
-      </c>
-      <c r="J24" s="32"/>
-      <c r="K24" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="L24" s="40"/>
-      <c r="M24" s="41"/>
-    </row>
-    <row r="25" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="37" t="s">
-        <v>248</v>
-      </c>
-      <c r="B25" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="C25" s="19" t="s">
-        <v>206</v>
-      </c>
-      <c r="D25" s="19" t="s">
-        <v>249</v>
-      </c>
-      <c r="E25" s="19" t="s">
-        <v>250</v>
-      </c>
-      <c r="F25" s="39" t="s">
-        <v>251</v>
-      </c>
-      <c r="G25" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="H25" s="39" t="s">
-        <v>253</v>
-      </c>
-      <c r="I25" s="33" t="s">
-        <v>113</v>
-      </c>
-      <c r="J25" s="39"/>
-      <c r="K25" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="L25" s="35"/>
-      <c r="M25" s="36"/>
-    </row>
-    <row r="26" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="30" t="s">
-        <v>254</v>
-      </c>
-      <c r="B26" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="C26" s="24" t="s">
-        <v>206</v>
-      </c>
-      <c r="D26" s="24" t="s">
-        <v>255</v>
-      </c>
-      <c r="E26" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="F26" s="32" t="s">
-        <v>257</v>
-      </c>
-      <c r="G26" s="24" t="s">
-        <v>258</v>
-      </c>
-      <c r="H26" s="32" t="s">
-        <v>259</v>
-      </c>
-      <c r="I26" s="33" t="s">
-        <v>113</v>
-      </c>
-      <c r="J26" s="32"/>
-      <c r="K26" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="L26" s="40"/>
-      <c r="M26" s="41"/>
-    </row>
-    <row r="27" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="37" t="s">
-        <v>260</v>
-      </c>
-      <c r="B27" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="C27" s="19" t="s">
-        <v>206</v>
-      </c>
-      <c r="D27" s="19" t="s">
-        <v>261</v>
-      </c>
-      <c r="E27" s="19" t="s">
-        <v>262</v>
-      </c>
-      <c r="F27" s="39" t="s">
-        <v>263</v>
-      </c>
-      <c r="G27" s="19" t="s">
-        <v>264</v>
-      </c>
-      <c r="H27" s="39" t="s">
-        <v>265</v>
-      </c>
-      <c r="I27" s="33" t="s">
-        <v>113</v>
-      </c>
-      <c r="J27" s="39"/>
-      <c r="K27" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="L27" s="35"/>
-      <c r="M27" s="36"/>
-    </row>
-    <row r="28" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="30" t="s">
-        <v>266</v>
-      </c>
-      <c r="B28" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="C28" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="D28" s="24" t="s">
-        <v>267</v>
-      </c>
-      <c r="E28" s="24" t="s">
-        <v>268</v>
-      </c>
-      <c r="F28" s="32" t="s">
-        <v>269</v>
-      </c>
-      <c r="G28" s="24" t="s">
-        <v>270</v>
-      </c>
-      <c r="H28" s="32" t="s">
-        <v>271</v>
-      </c>
-      <c r="I28" s="33" t="s">
-        <v>113</v>
-      </c>
-      <c r="J28" s="32"/>
-      <c r="K28" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="L28" s="40"/>
-      <c r="M28" s="41"/>
-    </row>
-    <row r="29" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="37" t="s">
-        <v>272</v>
-      </c>
-      <c r="B29" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="C29" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="D29" s="19" t="s">
-        <v>273</v>
-      </c>
-      <c r="E29" s="19" t="s">
-        <v>274</v>
-      </c>
-      <c r="F29" s="39" t="s">
-        <v>275</v>
-      </c>
-      <c r="G29" s="19" t="s">
-        <v>276</v>
-      </c>
-      <c r="H29" s="39" t="s">
-        <v>277</v>
-      </c>
-      <c r="I29" s="33" t="s">
-        <v>113</v>
-      </c>
-      <c r="J29" s="39"/>
-      <c r="K29" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="L29" s="35"/>
-      <c r="M29" s="36"/>
-    </row>
-    <row r="30" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="30" t="s">
-        <v>278</v>
-      </c>
-      <c r="B30" s="22" t="s">
-        <v>72</v>
-      </c>
-      <c r="C30" s="24" t="s">
-        <v>206</v>
-      </c>
-      <c r="D30" s="24" t="s">
-        <v>279</v>
-      </c>
-      <c r="E30" s="24" t="s">
-        <v>280</v>
-      </c>
-      <c r="F30" s="32" t="s">
-        <v>281</v>
-      </c>
-      <c r="G30" s="24" t="s">
-        <v>282</v>
-      </c>
-      <c r="H30" s="32" t="s">
-        <v>283</v>
-      </c>
-      <c r="I30" s="33" t="s">
-        <v>113</v>
-      </c>
-      <c r="J30" s="32"/>
-      <c r="K30" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="L30" s="40"/>
-      <c r="M30" s="41"/>
-    </row>
-    <row r="31" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="37" t="s">
-        <v>284</v>
-      </c>
-      <c r="B31" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="C31" s="19" t="s">
-        <v>206</v>
-      </c>
-      <c r="D31" s="19" t="s">
-        <v>285</v>
-      </c>
-      <c r="E31" s="19" t="s">
-        <v>286</v>
-      </c>
-      <c r="F31" s="39" t="s">
-        <v>287</v>
-      </c>
-      <c r="G31" s="19" t="s">
-        <v>288</v>
-      </c>
-      <c r="H31" s="39" t="s">
-        <v>289</v>
-      </c>
-      <c r="I31" s="33" t="s">
-        <v>113</v>
-      </c>
-      <c r="J31" s="39"/>
-      <c r="K31" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="L31" s="35"/>
-      <c r="M31" s="36"/>
-    </row>
-    <row r="32" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="30" t="s">
-        <v>290</v>
-      </c>
-      <c r="B32" s="22" t="s">
-        <v>76</v>
-      </c>
-      <c r="C32" s="24" t="s">
-        <v>206</v>
-      </c>
-      <c r="D32" s="24" t="s">
-        <v>291</v>
-      </c>
-      <c r="E32" s="24" t="s">
-        <v>292</v>
-      </c>
-      <c r="F32" s="32" t="s">
-        <v>293</v>
-      </c>
-      <c r="G32" s="24" t="s">
-        <v>294</v>
-      </c>
-      <c r="H32" s="32" t="s">
-        <v>295</v>
-      </c>
-      <c r="I32" s="33" t="s">
-        <v>113</v>
-      </c>
-      <c r="J32" s="32"/>
-      <c r="K32" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="L32" s="40"/>
-      <c r="M32" s="41"/>
-    </row>
-    <row r="33" spans="1:13" ht="109.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="37" t="s">
-        <v>296</v>
-      </c>
-      <c r="B33" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="C33" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="D33" s="19" t="s">
-        <v>297</v>
-      </c>
-      <c r="E33" s="19" t="s">
-        <v>298</v>
-      </c>
-      <c r="F33" s="39" t="s">
-        <v>299</v>
-      </c>
-      <c r="G33" s="19" t="s">
-        <v>300</v>
-      </c>
-      <c r="H33" s="39" t="s">
-        <v>301</v>
-      </c>
-      <c r="I33" s="33" t="s">
-        <v>113</v>
-      </c>
-      <c r="J33" s="39"/>
-      <c r="K33" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="L33" s="35"/>
-      <c r="M33" s="36"/>
-    </row>
-    <row r="34" spans="1:13" ht="99.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="30" t="s">
-        <v>302</v>
-      </c>
-      <c r="B34" s="22" t="s">
-        <v>84</v>
-      </c>
-      <c r="C34" s="24" t="s">
-        <v>206</v>
-      </c>
-      <c r="D34" s="24" t="s">
-        <v>303</v>
-      </c>
-      <c r="E34" s="24" t="s">
-        <v>304</v>
-      </c>
-      <c r="F34" s="32" t="s">
-        <v>305</v>
-      </c>
-      <c r="G34" s="24" t="s">
-        <v>306</v>
-      </c>
-      <c r="H34" s="32" t="s">
-        <v>307</v>
-      </c>
-      <c r="I34" s="33" t="s">
-        <v>113</v>
-      </c>
-      <c r="J34" s="32"/>
-      <c r="K34" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="L34" s="40"/>
-      <c r="M34" s="41"/>
+      <c r="I34" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="J34" s="30"/>
+      <c r="K34" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="L34" s="38"/>
+      <c r="M34" s="39"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:K2" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <mergeCells count="2">
+    <mergeCell ref="J1:K1"/>
     <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -3919,446 +4174,446 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="43" t="s">
+        <v>307</v>
+      </c>
+      <c r="B1" s="43" t="s">
         <v>308</v>
       </c>
-      <c r="B1" s="45" t="s">
+      <c r="C1" s="43" t="s">
         <v>309</v>
       </c>
-      <c r="C1" s="45" t="s">
+      <c r="D1" s="43" t="s">
         <v>310</v>
       </c>
-      <c r="D1" s="45" t="s">
+      <c r="E1" s="43" t="s">
         <v>311</v>
       </c>
-      <c r="E1" s="45" t="s">
+      <c r="F1" s="43" t="s">
         <v>312</v>
       </c>
-      <c r="F1" s="45" t="s">
+    </row>
+    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="44" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="46" t="s">
+      <c r="B2" s="45" t="s">
         <v>314</v>
       </c>
-      <c r="B2" s="47" t="s">
+      <c r="C2" s="45" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="46" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="47" t="s">
         <v>315</v>
       </c>
-      <c r="C2" s="47" t="s">
-        <v>39</v>
-      </c>
-      <c r="D2" s="48" t="s">
-        <v>107</v>
-      </c>
-      <c r="E2" s="49" t="s">
+      <c r="F2" s="46"/>
+    </row>
+    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="48"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="49" t="s">
+        <v>315</v>
+      </c>
+      <c r="F3" s="46"/>
+    </row>
+    <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="48"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="49" t="s">
+        <v>315</v>
+      </c>
+      <c r="F4" s="46"/>
+    </row>
+    <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="48"/>
+      <c r="B5" s="46"/>
+      <c r="C5" s="46"/>
+      <c r="D5" s="46" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" s="49" t="s">
+        <v>315</v>
+      </c>
+      <c r="F5" s="46"/>
+    </row>
+    <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="48"/>
+      <c r="B6" s="46"/>
+      <c r="C6" s="46"/>
+      <c r="D6" s="46" t="s">
+        <v>49</v>
+      </c>
+      <c r="E6" s="50" t="s">
         <v>316</v>
       </c>
-      <c r="F2" s="48"/>
-    </row>
-    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="50"/>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48" t="s">
+      <c r="F6" s="46" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="48"/>
+      <c r="B7" s="46"/>
+      <c r="C7" s="45" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" s="46" t="s">
+        <v>56</v>
+      </c>
+      <c r="E7" s="49" t="s">
+        <v>315</v>
+      </c>
+      <c r="F7" s="46"/>
+    </row>
+    <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="48"/>
+      <c r="B8" s="46"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46" t="s">
+        <v>64</v>
+      </c>
+      <c r="E8" s="49" t="s">
+        <v>315</v>
+      </c>
+      <c r="F8" s="46"/>
+    </row>
+    <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="48"/>
+      <c r="B9" s="46"/>
+      <c r="C9" s="46"/>
+      <c r="D9" s="46" t="s">
+        <v>70</v>
+      </c>
+      <c r="E9" s="49" t="s">
+        <v>315</v>
+      </c>
+      <c r="F9" s="46"/>
+    </row>
+    <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="48"/>
+      <c r="B10" s="46"/>
+      <c r="C10" s="45" t="s">
+        <v>77</v>
+      </c>
+      <c r="D10" s="46" t="s">
+        <v>76</v>
+      </c>
+      <c r="E10" s="49" t="s">
+        <v>315</v>
+      </c>
+      <c r="F10" s="46"/>
+    </row>
+    <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="48"/>
+      <c r="B11" s="46"/>
+      <c r="C11" s="46"/>
+      <c r="D11" s="46" t="s">
+        <v>84</v>
+      </c>
+      <c r="E11" s="49" t="s">
+        <v>315</v>
+      </c>
+      <c r="F11" s="46"/>
+    </row>
+    <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="48"/>
+      <c r="B12" s="46"/>
+      <c r="C12" s="46"/>
+      <c r="D12" s="46" t="s">
+        <v>90</v>
+      </c>
+      <c r="E12" s="49" t="s">
+        <v>315</v>
+      </c>
+      <c r="F12" s="46"/>
+    </row>
+    <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="48"/>
+      <c r="B13" s="46"/>
+      <c r="C13" s="46"/>
+      <c r="D13" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="E13" s="49" t="s">
+        <v>315</v>
+      </c>
+      <c r="F13" s="46"/>
+    </row>
+    <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="48"/>
+      <c r="B14" s="46"/>
+      <c r="C14" s="46"/>
+      <c r="D14" s="46" t="s">
+        <v>102</v>
+      </c>
+      <c r="E14" s="49" t="s">
+        <v>315</v>
+      </c>
+      <c r="F14" s="46"/>
+    </row>
+    <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="48"/>
+      <c r="B15" s="46"/>
+      <c r="C15" s="45" t="s">
+        <v>109</v>
+      </c>
+      <c r="D15" s="46" t="s">
+        <v>108</v>
+      </c>
+      <c r="E15" s="49" t="s">
+        <v>315</v>
+      </c>
+      <c r="F15" s="46"/>
+    </row>
+    <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="48"/>
+      <c r="B16" s="46"/>
+      <c r="C16" s="46"/>
+      <c r="D16" s="46" t="s">
         <v>115</v>
       </c>
-      <c r="E3" s="51" t="s">
-        <v>316</v>
-      </c>
-      <c r="F3" s="48"/>
-    </row>
-    <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="50"/>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48" t="s">
-        <v>122</v>
-      </c>
-      <c r="E4" s="51" t="s">
-        <v>316</v>
-      </c>
-      <c r="F4" s="48"/>
-    </row>
-    <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="50"/>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48" t="s">
+      <c r="E16" s="49" t="s">
+        <v>315</v>
+      </c>
+      <c r="F16" s="46"/>
+    </row>
+    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="48"/>
+      <c r="B17" s="46"/>
+      <c r="C17" s="46"/>
+      <c r="D17" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="E17" s="49" t="s">
+        <v>315</v>
+      </c>
+      <c r="F17" s="46"/>
+    </row>
+    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="44" t="s">
+        <v>318</v>
+      </c>
+      <c r="B18" s="45" t="s">
+        <v>319</v>
+      </c>
+      <c r="C18" s="45" t="s">
+        <v>129</v>
+      </c>
+      <c r="D18" s="46" t="s">
         <v>128</v>
       </c>
-      <c r="E5" s="51" t="s">
-        <v>316</v>
-      </c>
-      <c r="F5" s="48"/>
-    </row>
-    <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="50"/>
-      <c r="B6" s="48"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="48" t="s">
+      <c r="E18" s="49" t="s">
+        <v>315</v>
+      </c>
+      <c r="F18" s="46"/>
+    </row>
+    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="48"/>
+      <c r="B19" s="46"/>
+      <c r="C19" s="46"/>
+      <c r="D19" s="46" t="s">
         <v>135</v>
       </c>
-      <c r="E6" s="52" t="s">
-        <v>317</v>
-      </c>
-      <c r="F6" s="48" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="50"/>
-      <c r="B7" s="48"/>
-      <c r="C7" s="47" t="s">
-        <v>44</v>
-      </c>
-      <c r="D7" s="48" t="s">
-        <v>143</v>
-      </c>
-      <c r="E7" s="51" t="s">
-        <v>316</v>
-      </c>
-      <c r="F7" s="48"/>
-    </row>
-    <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="50"/>
-      <c r="B8" s="48"/>
-      <c r="C8" s="48"/>
-      <c r="D8" s="48" t="s">
-        <v>150</v>
-      </c>
-      <c r="E8" s="51" t="s">
-        <v>316</v>
-      </c>
-      <c r="F8" s="48"/>
-    </row>
-    <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="50"/>
-      <c r="B9" s="48"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="48" t="s">
-        <v>156</v>
-      </c>
-      <c r="E9" s="51" t="s">
-        <v>316</v>
-      </c>
-      <c r="F9" s="48"/>
-    </row>
-    <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="50"/>
-      <c r="B10" s="48"/>
-      <c r="C10" s="47" t="s">
-        <v>48</v>
-      </c>
-      <c r="D10" s="48" t="s">
-        <v>162</v>
-      </c>
-      <c r="E10" s="51" t="s">
-        <v>316</v>
-      </c>
-      <c r="F10" s="48"/>
-    </row>
-    <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="50"/>
-      <c r="B11" s="48"/>
-      <c r="C11" s="48"/>
-      <c r="D11" s="48" t="s">
-        <v>169</v>
-      </c>
-      <c r="E11" s="51" t="s">
-        <v>316</v>
-      </c>
-      <c r="F11" s="48"/>
-    </row>
-    <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="50"/>
-      <c r="B12" s="48"/>
-      <c r="C12" s="48"/>
-      <c r="D12" s="48" t="s">
-        <v>175</v>
-      </c>
-      <c r="E12" s="51" t="s">
-        <v>316</v>
-      </c>
-      <c r="F12" s="48"/>
-    </row>
-    <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="50"/>
-      <c r="B13" s="48"/>
-      <c r="C13" s="48"/>
-      <c r="D13" s="48" t="s">
-        <v>181</v>
-      </c>
-      <c r="E13" s="51" t="s">
-        <v>316</v>
-      </c>
-      <c r="F13" s="48"/>
-    </row>
-    <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="50"/>
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="48" t="s">
-        <v>187</v>
-      </c>
-      <c r="E14" s="51" t="s">
-        <v>316</v>
-      </c>
-      <c r="F14" s="48"/>
-    </row>
-    <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="50"/>
-      <c r="B15" s="48"/>
-      <c r="C15" s="47" t="s">
-        <v>52</v>
-      </c>
-      <c r="D15" s="48" t="s">
+      <c r="E19" s="49" t="s">
+        <v>315</v>
+      </c>
+      <c r="F19" s="46"/>
+    </row>
+    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="48"/>
+      <c r="B20" s="46"/>
+      <c r="C20" s="46"/>
+      <c r="D20" s="46" t="s">
+        <v>141</v>
+      </c>
+      <c r="E20" s="49" t="s">
+        <v>315</v>
+      </c>
+      <c r="F20" s="46"/>
+    </row>
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="48"/>
+      <c r="B21" s="46"/>
+      <c r="C21" s="46"/>
+      <c r="D21" s="46" t="s">
+        <v>147</v>
+      </c>
+      <c r="E21" s="49" t="s">
+        <v>315</v>
+      </c>
+      <c r="F21" s="46"/>
+    </row>
+    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="48"/>
+      <c r="B22" s="46"/>
+      <c r="C22" s="45" t="s">
+        <v>154</v>
+      </c>
+      <c r="D22" s="46" t="s">
+        <v>153</v>
+      </c>
+      <c r="E22" s="49" t="s">
+        <v>315</v>
+      </c>
+      <c r="F22" s="46"/>
+    </row>
+    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="48"/>
+      <c r="B23" s="46"/>
+      <c r="C23" s="46"/>
+      <c r="D23" s="46" t="s">
+        <v>160</v>
+      </c>
+      <c r="E23" s="49" t="s">
+        <v>315</v>
+      </c>
+      <c r="F23" s="46"/>
+    </row>
+    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="48"/>
+      <c r="B24" s="46"/>
+      <c r="C24" s="46"/>
+      <c r="D24" s="46" t="s">
+        <v>166</v>
+      </c>
+      <c r="E24" s="49" t="s">
+        <v>315</v>
+      </c>
+      <c r="F24" s="46"/>
+    </row>
+    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="48"/>
+      <c r="B25" s="46"/>
+      <c r="C25" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="D25" s="46" t="s">
+        <v>172</v>
+      </c>
+      <c r="E25" s="49" t="s">
+        <v>315</v>
+      </c>
+      <c r="F25" s="46"/>
+    </row>
+    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="48"/>
+      <c r="B26" s="46"/>
+      <c r="C26" s="46"/>
+      <c r="D26" s="46" t="s">
+        <v>179</v>
+      </c>
+      <c r="E26" s="49" t="s">
+        <v>315</v>
+      </c>
+      <c r="F26" s="46"/>
+    </row>
+    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="48"/>
+      <c r="B27" s="46"/>
+      <c r="C27" s="45" t="s">
+        <v>186</v>
+      </c>
+      <c r="D27" s="46" t="s">
+        <v>185</v>
+      </c>
+      <c r="E27" s="49" t="s">
+        <v>315</v>
+      </c>
+      <c r="F27" s="46"/>
+    </row>
+    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="44" t="s">
+        <v>320</v>
+      </c>
+      <c r="B28" s="45" t="s">
+        <v>321</v>
+      </c>
+      <c r="C28" s="45" t="s">
         <v>193</v>
       </c>
-      <c r="E15" s="51" t="s">
-        <v>316</v>
-      </c>
-      <c r="F15" s="48"/>
-    </row>
-    <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="50"/>
-      <c r="B16" s="48"/>
-      <c r="C16" s="48"/>
-      <c r="D16" s="48" t="s">
+      <c r="D28" s="46" t="s">
+        <v>192</v>
+      </c>
+      <c r="E28" s="49" t="s">
+        <v>315</v>
+      </c>
+      <c r="F28" s="46"/>
+    </row>
+    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="48"/>
+      <c r="B29" s="46"/>
+      <c r="C29" s="46"/>
+      <c r="D29" s="46" t="s">
         <v>199</v>
       </c>
-      <c r="E16" s="51" t="s">
-        <v>316</v>
-      </c>
-      <c r="F16" s="48"/>
-    </row>
-    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="50"/>
-      <c r="B17" s="48"/>
-      <c r="C17" s="48"/>
-      <c r="D17" s="48" t="s">
+      <c r="E29" s="49" t="s">
+        <v>315</v>
+      </c>
+      <c r="F29" s="46"/>
+    </row>
+    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="48"/>
+      <c r="B30" s="46"/>
+      <c r="C30" s="45" t="s">
+        <v>206</v>
+      </c>
+      <c r="D30" s="46" t="s">
         <v>205</v>
       </c>
-      <c r="E17" s="51" t="s">
-        <v>316</v>
-      </c>
-      <c r="F17" s="48"/>
-    </row>
-    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="46" t="s">
-        <v>319</v>
-      </c>
-      <c r="B18" s="47" t="s">
-        <v>320</v>
-      </c>
-      <c r="C18" s="47" t="s">
-        <v>56</v>
-      </c>
-      <c r="D18" s="48" t="s">
+      <c r="E30" s="49" t="s">
+        <v>315</v>
+      </c>
+      <c r="F30" s="46"/>
+    </row>
+    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="48"/>
+      <c r="B31" s="46"/>
+      <c r="C31" s="46"/>
+      <c r="D31" s="46" t="s">
         <v>212</v>
       </c>
-      <c r="E18" s="51" t="s">
-        <v>316</v>
-      </c>
-      <c r="F18" s="48"/>
-    </row>
-    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="50"/>
-      <c r="B19" s="48"/>
-      <c r="C19" s="48"/>
-      <c r="D19" s="48" t="s">
+      <c r="E31" s="49" t="s">
+        <v>315</v>
+      </c>
+      <c r="F31" s="46"/>
+    </row>
+    <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="48"/>
+      <c r="B32" s="46"/>
+      <c r="C32" s="45" t="s">
+        <v>219</v>
+      </c>
+      <c r="D32" s="46" t="s">
         <v>218</v>
       </c>
-      <c r="E19" s="51" t="s">
-        <v>316</v>
-      </c>
-      <c r="F19" s="48"/>
-    </row>
-    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="50"/>
-      <c r="B20" s="48"/>
-      <c r="C20" s="48"/>
-      <c r="D20" s="48" t="s">
-        <v>224</v>
-      </c>
-      <c r="E20" s="51" t="s">
-        <v>316</v>
-      </c>
-      <c r="F20" s="48"/>
-    </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="50"/>
-      <c r="B21" s="48"/>
-      <c r="C21" s="48"/>
-      <c r="D21" s="48" t="s">
-        <v>230</v>
-      </c>
-      <c r="E21" s="51" t="s">
-        <v>316</v>
-      </c>
-      <c r="F21" s="48"/>
-    </row>
-    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="50"/>
-      <c r="B22" s="48"/>
-      <c r="C22" s="47" t="s">
-        <v>60</v>
-      </c>
-      <c r="D22" s="48" t="s">
-        <v>236</v>
-      </c>
-      <c r="E22" s="51" t="s">
-        <v>316</v>
-      </c>
-      <c r="F22" s="48"/>
-    </row>
-    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="50"/>
-      <c r="B23" s="48"/>
-      <c r="C23" s="48"/>
-      <c r="D23" s="48" t="s">
-        <v>242</v>
-      </c>
-      <c r="E23" s="51" t="s">
-        <v>316</v>
-      </c>
-      <c r="F23" s="48"/>
-    </row>
-    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="50"/>
-      <c r="B24" s="48"/>
-      <c r="C24" s="48"/>
-      <c r="D24" s="48" t="s">
-        <v>248</v>
-      </c>
-      <c r="E24" s="51" t="s">
-        <v>316</v>
-      </c>
-      <c r="F24" s="48"/>
-    </row>
-    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="50"/>
-      <c r="B25" s="48"/>
-      <c r="C25" s="47" t="s">
-        <v>64</v>
-      </c>
-      <c r="D25" s="48" t="s">
-        <v>254</v>
-      </c>
-      <c r="E25" s="51" t="s">
-        <v>316</v>
-      </c>
-      <c r="F25" s="48"/>
-    </row>
-    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="50"/>
-      <c r="B26" s="48"/>
-      <c r="C26" s="48"/>
-      <c r="D26" s="48" t="s">
-        <v>260</v>
-      </c>
-      <c r="E26" s="51" t="s">
-        <v>316</v>
-      </c>
-      <c r="F26" s="48"/>
-    </row>
-    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="50"/>
-      <c r="B27" s="48"/>
-      <c r="C27" s="47" t="s">
-        <v>68</v>
-      </c>
-      <c r="D27" s="48" t="s">
-        <v>266</v>
-      </c>
-      <c r="E27" s="51" t="s">
-        <v>316</v>
-      </c>
-      <c r="F27" s="48"/>
-    </row>
-    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="46" t="s">
-        <v>321</v>
-      </c>
-      <c r="B28" s="47" t="s">
-        <v>322</v>
-      </c>
-      <c r="C28" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="D28" s="48" t="s">
-        <v>272</v>
-      </c>
-      <c r="E28" s="51" t="s">
-        <v>316</v>
-      </c>
-      <c r="F28" s="48"/>
-    </row>
-    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="50"/>
-      <c r="B29" s="48"/>
-      <c r="C29" s="48"/>
-      <c r="D29" s="48" t="s">
-        <v>278</v>
-      </c>
-      <c r="E29" s="51" t="s">
-        <v>316</v>
-      </c>
-      <c r="F29" s="48"/>
-    </row>
-    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="50"/>
-      <c r="B30" s="48"/>
-      <c r="C30" s="47" t="s">
-        <v>76</v>
-      </c>
-      <c r="D30" s="48" t="s">
-        <v>284</v>
-      </c>
-      <c r="E30" s="51" t="s">
-        <v>316</v>
-      </c>
-      <c r="F30" s="48"/>
-    </row>
-    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="50"/>
-      <c r="B31" s="48"/>
-      <c r="C31" s="48"/>
-      <c r="D31" s="48" t="s">
-        <v>290</v>
-      </c>
-      <c r="E31" s="51" t="s">
-        <v>316</v>
-      </c>
-      <c r="F31" s="48"/>
-    </row>
-    <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="50"/>
-      <c r="B32" s="48"/>
-      <c r="C32" s="47" t="s">
-        <v>80</v>
-      </c>
-      <c r="D32" s="48" t="s">
-        <v>296</v>
-      </c>
-      <c r="E32" s="51" t="s">
-        <v>316</v>
-      </c>
-      <c r="F32" s="48"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A33" s="50"/>
-      <c r="B33" s="48"/>
-      <c r="C33" s="47" t="s">
-        <v>84</v>
-      </c>
-      <c r="D33" s="48" t="s">
-        <v>302</v>
-      </c>
-      <c r="E33" s="51" t="s">
-        <v>316</v>
-      </c>
-      <c r="F33" s="48"/>
+      <c r="E32" s="49" t="s">
+        <v>315</v>
+      </c>
+      <c r="F32" s="46"/>
+    </row>
+    <row r="33" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="48"/>
+      <c r="B33" s="46"/>
+      <c r="C33" s="45" t="s">
+        <v>226</v>
+      </c>
+      <c r="D33" s="46" t="s">
+        <v>225</v>
+      </c>
+      <c r="E33" s="49" t="s">
+        <v>315</v>
+      </c>
+      <c r="F33" s="46"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4380,47 +4635,468 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="51" t="s">
+        <v>322</v>
+      </c>
+      <c r="B1" s="51" t="s">
         <v>323</v>
       </c>
-      <c r="B1" s="53" t="s">
+      <c r="C1" s="51" t="s">
         <v>324</v>
       </c>
-      <c r="C1" s="53" t="s">
+      <c r="D1" s="51" t="s">
         <v>325</v>
       </c>
-      <c r="D1" s="53" t="s">
+      <c r="E1" s="51" t="s">
         <v>326</v>
       </c>
-      <c r="E1" s="53" t="s">
+      <c r="F1" s="51" t="s">
         <v>327</v>
       </c>
-      <c r="F1" s="53" t="s">
+    </row>
+    <row r="2" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="52" t="s">
+        <v>317</v>
+      </c>
+      <c r="B2" s="52" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="54" t="s">
-        <v>318</v>
-      </c>
-      <c r="B2" s="54" t="s">
+      <c r="C2" s="53" t="s">
         <v>329</v>
       </c>
-      <c r="C2" s="55" t="s">
+      <c r="D2" s="52" t="s">
+        <v>237</v>
+      </c>
+      <c r="E2" s="76" t="s">
+        <v>360</v>
+      </c>
+      <c r="F2" s="52" t="s">
         <v>330</v>
       </c>
-      <c r="D2" s="54" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="54" t="s">
-        <v>331</v>
-      </c>
-      <c r="F2" s="54" t="s">
-        <v>332</v>
-      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{1A197657-F570-4A6C-95EA-50684754A62C}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="52" customWidth="1"/>
+    <col min="3" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="7" max="8" width="17" customWidth="1"/>
+    <col min="9" max="9" width="22" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="71" t="s">
+        <v>331</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+    </row>
+    <row r="2" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="54" t="s">
+        <v>332</v>
+      </c>
+      <c r="B2" s="54" t="s">
+        <v>333</v>
+      </c>
+      <c r="C2" s="54" t="s">
+        <v>334</v>
+      </c>
+      <c r="D2" s="54" t="s">
+        <v>335</v>
+      </c>
+      <c r="E2" s="54" t="s">
+        <v>336</v>
+      </c>
+      <c r="F2" s="54" t="s">
+        <v>337</v>
+      </c>
+      <c r="G2" s="54" t="s">
+        <v>338</v>
+      </c>
+      <c r="H2" s="54" t="s">
+        <v>339</v>
+      </c>
+      <c r="I2" s="54" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="73" t="s">
+        <v>328</v>
+      </c>
+      <c r="B3" s="55" t="s">
+        <v>341</v>
+      </c>
+      <c r="C3" s="56">
+        <v>5</v>
+      </c>
+      <c r="D3" s="57">
+        <v>4</v>
+      </c>
+      <c r="E3" s="58">
+        <v>1</v>
+      </c>
+      <c r="F3" s="56">
+        <v>5</v>
+      </c>
+      <c r="G3" s="56" t="s">
+        <v>342</v>
+      </c>
+      <c r="H3" s="56" t="s">
+        <v>343</v>
+      </c>
+      <c r="I3" s="56" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="74"/>
+      <c r="B4" s="59" t="s">
+        <v>345</v>
+      </c>
+      <c r="C4" s="60">
+        <v>3</v>
+      </c>
+      <c r="D4" s="61">
+        <v>3</v>
+      </c>
+      <c r="E4" s="62">
+        <v>0</v>
+      </c>
+      <c r="F4" s="60">
+        <v>3</v>
+      </c>
+      <c r="G4" s="60" t="s">
+        <v>344</v>
+      </c>
+      <c r="H4" s="60" t="s">
+        <v>346</v>
+      </c>
+      <c r="I4" s="60" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="74"/>
+      <c r="B5" s="55" t="s">
+        <v>347</v>
+      </c>
+      <c r="C5" s="56">
+        <v>5</v>
+      </c>
+      <c r="D5" s="57">
+        <v>5</v>
+      </c>
+      <c r="E5" s="63">
+        <v>0</v>
+      </c>
+      <c r="F5" s="56">
+        <v>5</v>
+      </c>
+      <c r="G5" s="56" t="s">
+        <v>344</v>
+      </c>
+      <c r="H5" s="56" t="s">
+        <v>346</v>
+      </c>
+      <c r="I5" s="56" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="74"/>
+      <c r="B6" s="59" t="s">
+        <v>348</v>
+      </c>
+      <c r="C6" s="60">
+        <v>3</v>
+      </c>
+      <c r="D6" s="61">
+        <v>3</v>
+      </c>
+      <c r="E6" s="62">
+        <v>0</v>
+      </c>
+      <c r="F6" s="60">
+        <v>3</v>
+      </c>
+      <c r="G6" s="60" t="s">
+        <v>344</v>
+      </c>
+      <c r="H6" s="60" t="s">
+        <v>346</v>
+      </c>
+      <c r="I6" s="60" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="74"/>
+      <c r="B7" s="55" t="s">
+        <v>349</v>
+      </c>
+      <c r="C7" s="56">
+        <v>4</v>
+      </c>
+      <c r="D7" s="57">
+        <v>4</v>
+      </c>
+      <c r="E7" s="63">
+        <v>0</v>
+      </c>
+      <c r="F7" s="56">
+        <v>4</v>
+      </c>
+      <c r="G7" s="56" t="s">
+        <v>344</v>
+      </c>
+      <c r="H7" s="56" t="s">
+        <v>346</v>
+      </c>
+      <c r="I7" s="56" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="74"/>
+      <c r="B8" s="59" t="s">
+        <v>350</v>
+      </c>
+      <c r="C8" s="60">
+        <v>3</v>
+      </c>
+      <c r="D8" s="61">
+        <v>3</v>
+      </c>
+      <c r="E8" s="62">
+        <v>0</v>
+      </c>
+      <c r="F8" s="60">
+        <v>3</v>
+      </c>
+      <c r="G8" s="60" t="s">
+        <v>344</v>
+      </c>
+      <c r="H8" s="60" t="s">
+        <v>346</v>
+      </c>
+      <c r="I8" s="60" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="74"/>
+      <c r="B9" s="55" t="s">
+        <v>351</v>
+      </c>
+      <c r="C9" s="56">
+        <v>2</v>
+      </c>
+      <c r="D9" s="57">
+        <v>2</v>
+      </c>
+      <c r="E9" s="63">
+        <v>0</v>
+      </c>
+      <c r="F9" s="56">
+        <v>2</v>
+      </c>
+      <c r="G9" s="56" t="s">
+        <v>344</v>
+      </c>
+      <c r="H9" s="56" t="s">
+        <v>346</v>
+      </c>
+      <c r="I9" s="56" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="74"/>
+      <c r="B10" s="59" t="s">
+        <v>352</v>
+      </c>
+      <c r="C10" s="60">
+        <v>1</v>
+      </c>
+      <c r="D10" s="61">
+        <v>1</v>
+      </c>
+      <c r="E10" s="62">
+        <v>0</v>
+      </c>
+      <c r="F10" s="60">
+        <v>1</v>
+      </c>
+      <c r="G10" s="60" t="s">
+        <v>344</v>
+      </c>
+      <c r="H10" s="60" t="s">
+        <v>346</v>
+      </c>
+      <c r="I10" s="60" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="74"/>
+      <c r="B11" s="55" t="s">
+        <v>353</v>
+      </c>
+      <c r="C11" s="56">
+        <v>2</v>
+      </c>
+      <c r="D11" s="57">
+        <v>2</v>
+      </c>
+      <c r="E11" s="63">
+        <v>0</v>
+      </c>
+      <c r="F11" s="56">
+        <v>2</v>
+      </c>
+      <c r="G11" s="56" t="s">
+        <v>344</v>
+      </c>
+      <c r="H11" s="56" t="s">
+        <v>346</v>
+      </c>
+      <c r="I11" s="56" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="74"/>
+      <c r="B12" s="59" t="s">
+        <v>354</v>
+      </c>
+      <c r="C12" s="60">
+        <v>2</v>
+      </c>
+      <c r="D12" s="61">
+        <v>2</v>
+      </c>
+      <c r="E12" s="62">
+        <v>0</v>
+      </c>
+      <c r="F12" s="60">
+        <v>2</v>
+      </c>
+      <c r="G12" s="60" t="s">
+        <v>344</v>
+      </c>
+      <c r="H12" s="60" t="s">
+        <v>346</v>
+      </c>
+      <c r="I12" s="60" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="74"/>
+      <c r="B13" s="55" t="s">
+        <v>355</v>
+      </c>
+      <c r="C13" s="56">
+        <v>1</v>
+      </c>
+      <c r="D13" s="57">
+        <v>1</v>
+      </c>
+      <c r="E13" s="63">
+        <v>0</v>
+      </c>
+      <c r="F13" s="56">
+        <v>1</v>
+      </c>
+      <c r="G13" s="56" t="s">
+        <v>344</v>
+      </c>
+      <c r="H13" s="56" t="s">
+        <v>346</v>
+      </c>
+      <c r="I13" s="56" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="75"/>
+      <c r="B14" s="59" t="s">
+        <v>356</v>
+      </c>
+      <c r="C14" s="60">
+        <v>1</v>
+      </c>
+      <c r="D14" s="61">
+        <v>1</v>
+      </c>
+      <c r="E14" s="62">
+        <v>0</v>
+      </c>
+      <c r="F14" s="60">
+        <v>1</v>
+      </c>
+      <c r="G14" s="60" t="s">
+        <v>344</v>
+      </c>
+      <c r="H14" s="60" t="s">
+        <v>346</v>
+      </c>
+      <c r="I14" s="60" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="72" t="s">
+        <v>357</v>
+      </c>
+      <c r="B15" s="70"/>
+      <c r="C15" s="64">
+        <v>32</v>
+      </c>
+      <c r="D15" s="65">
+        <v>31</v>
+      </c>
+      <c r="E15" s="66">
+        <v>1</v>
+      </c>
+      <c r="F15" s="64">
+        <v>32</v>
+      </c>
+      <c r="G15" s="64" t="s">
+        <v>358</v>
+      </c>
+      <c r="H15" s="64" t="s">
+        <v>359</v>
+      </c>
+      <c r="I15" s="64" t="s">
+        <v>344</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A3:A14"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Ritam_Bhattachrya_RedBus/Epic3.xlsx
+++ b/Ritam_Bhattachrya_RedBus/Epic3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ritam\Programming\Capgemini_Sprint\Ritam_Bhattachrya_RedBus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56EFCB2E-625B-4593-951E-C025BCB3EC46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BEFF942-676D-48C7-9C3F-19CC60C79BFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" tabRatio="500" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2097,6 +2097,9 @@
     <xf numFmtId="0" fontId="32" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2116,9 +2119,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2573,10 +2573,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="70" t="s">
         <v>256</v>
       </c>
-      <c r="B1" s="70"/>
+      <c r="B1" s="71"/>
     </row>
     <row r="2" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
@@ -2931,7 +2931,7 @@
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="2" max="2" width="23.26953125" customWidth="1"/>
     <col min="3" max="3" width="44" customWidth="1"/>
     <col min="4" max="4" width="40" customWidth="1"/>
     <col min="5" max="5" width="58" customWidth="1"/>
@@ -2967,14 +2967,14 @@
       <c r="G1" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="67" t="s">
+      <c r="H1" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="68"/>
-      <c r="J1" s="67" t="s">
+      <c r="I1" s="69"/>
+      <c r="J1" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="68"/>
+      <c r="K1" s="69"/>
       <c r="L1" s="25" t="s">
         <v>9</v>
       </c>
@@ -4667,7 +4667,7 @@
       <c r="D2" s="52" t="s">
         <v>237</v>
       </c>
-      <c r="E2" s="76" t="s">
+      <c r="E2" s="67" t="s">
         <v>360</v>
       </c>
       <c r="F2" s="52" t="s">
@@ -4697,17 +4697,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="72" t="s">
         <v>331</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="70"/>
-      <c r="I1" s="70"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="71"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="54" t="s">
@@ -4739,7 +4739,7 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="73" t="s">
+      <c r="A3" s="74" t="s">
         <v>328</v>
       </c>
       <c r="B3" s="55" t="s">
@@ -4768,7 +4768,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="74"/>
+      <c r="A4" s="75"/>
       <c r="B4" s="59" t="s">
         <v>345</v>
       </c>
@@ -4795,7 +4795,7 @@
       </c>
     </row>
     <row r="5" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="74"/>
+      <c r="A5" s="75"/>
       <c r="B5" s="55" t="s">
         <v>347</v>
       </c>
@@ -4822,7 +4822,7 @@
       </c>
     </row>
     <row r="6" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="74"/>
+      <c r="A6" s="75"/>
       <c r="B6" s="59" t="s">
         <v>348</v>
       </c>
@@ -4849,7 +4849,7 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="74"/>
+      <c r="A7" s="75"/>
       <c r="B7" s="55" t="s">
         <v>349</v>
       </c>
@@ -4876,7 +4876,7 @@
       </c>
     </row>
     <row r="8" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="74"/>
+      <c r="A8" s="75"/>
       <c r="B8" s="59" t="s">
         <v>350</v>
       </c>
@@ -4903,7 +4903,7 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="74"/>
+      <c r="A9" s="75"/>
       <c r="B9" s="55" t="s">
         <v>351</v>
       </c>
@@ -4930,7 +4930,7 @@
       </c>
     </row>
     <row r="10" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="74"/>
+      <c r="A10" s="75"/>
       <c r="B10" s="59" t="s">
         <v>352</v>
       </c>
@@ -4957,7 +4957,7 @@
       </c>
     </row>
     <row r="11" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="74"/>
+      <c r="A11" s="75"/>
       <c r="B11" s="55" t="s">
         <v>353</v>
       </c>
@@ -4984,7 +4984,7 @@
       </c>
     </row>
     <row r="12" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="74"/>
+      <c r="A12" s="75"/>
       <c r="B12" s="59" t="s">
         <v>354</v>
       </c>
@@ -5011,7 +5011,7 @@
       </c>
     </row>
     <row r="13" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="74"/>
+      <c r="A13" s="75"/>
       <c r="B13" s="55" t="s">
         <v>355</v>
       </c>
@@ -5038,7 +5038,7 @@
       </c>
     </row>
     <row r="14" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="75"/>
+      <c r="A14" s="76"/>
       <c r="B14" s="59" t="s">
         <v>356</v>
       </c>
@@ -5065,10 +5065,10 @@
       </c>
     </row>
     <row r="15" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="72" t="s">
+      <c r="A15" s="73" t="s">
         <v>357</v>
       </c>
-      <c r="B15" s="70"/>
+      <c r="B15" s="71"/>
       <c r="C15" s="64">
         <v>32</v>
       </c>

--- a/Ritam_Bhattachrya_RedBus/Epic3.xlsx
+++ b/Ritam_Bhattachrya_RedBus/Epic3.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ritam\Programming\Capgemini_Sprint\Ritam_Bhattachrya_RedBus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BEFF942-676D-48C7-9C3F-19CC60C79BFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E635ED8-40CC-441E-A23E-205325386595}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" tabRatio="500" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" tabRatio="500" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Train Search &amp; Filter" sheetId="1" r:id="rId1"/>
     <sheet name="Summary" sheetId="2" r:id="rId2"/>
     <sheet name="Test Scenarios" sheetId="3" r:id="rId3"/>
     <sheet name="Test Cases" sheetId="4" r:id="rId4"/>
-    <sheet name="RTM" sheetId="5" r:id="rId5"/>
-    <sheet name="Defect Report" sheetId="6" r:id="rId6"/>
+    <sheet name="Defect Report" sheetId="6" r:id="rId5"/>
+    <sheet name="RTM" sheetId="5" r:id="rId6"/>
     <sheet name="Test Execution Summary" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
@@ -4161,6 +4161,68 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.81640625" customWidth="1"/>
+    <col min="2" max="2" width="17.54296875" customWidth="1"/>
+    <col min="3" max="3" width="55" customWidth="1"/>
+    <col min="4" max="4" width="17.453125" customWidth="1"/>
+    <col min="5" max="5" width="29.453125" customWidth="1"/>
+    <col min="6" max="6" width="13.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="51" t="s">
+        <v>322</v>
+      </c>
+      <c r="B1" s="51" t="s">
+        <v>323</v>
+      </c>
+      <c r="C1" s="51" t="s">
+        <v>324</v>
+      </c>
+      <c r="D1" s="51" t="s">
+        <v>325</v>
+      </c>
+      <c r="E1" s="51" t="s">
+        <v>326</v>
+      </c>
+      <c r="F1" s="51" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="52" t="s">
+        <v>317</v>
+      </c>
+      <c r="B2" s="52" t="s">
+        <v>328</v>
+      </c>
+      <c r="C2" s="53" t="s">
+        <v>329</v>
+      </c>
+      <c r="D2" s="52" t="s">
+        <v>237</v>
+      </c>
+      <c r="E2" s="67" t="s">
+        <v>360</v>
+      </c>
+      <c r="F2" s="52" t="s">
+        <v>330</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{1A197657-F570-4A6C-95EA-50684754A62C}"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F33"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -4616,68 +4678,6 @@
       <c r="F33" s="46"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="17.81640625" customWidth="1"/>
-    <col min="2" max="2" width="17.54296875" customWidth="1"/>
-    <col min="3" max="3" width="55" customWidth="1"/>
-    <col min="4" max="4" width="17.453125" customWidth="1"/>
-    <col min="5" max="5" width="29.453125" customWidth="1"/>
-    <col min="6" max="6" width="13.54296875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="51" t="s">
-        <v>322</v>
-      </c>
-      <c r="B1" s="51" t="s">
-        <v>323</v>
-      </c>
-      <c r="C1" s="51" t="s">
-        <v>324</v>
-      </c>
-      <c r="D1" s="51" t="s">
-        <v>325</v>
-      </c>
-      <c r="E1" s="51" t="s">
-        <v>326</v>
-      </c>
-      <c r="F1" s="51" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="52" t="s">
-        <v>317</v>
-      </c>
-      <c r="B2" s="52" t="s">
-        <v>328</v>
-      </c>
-      <c r="C2" s="53" t="s">
-        <v>329</v>
-      </c>
-      <c r="D2" s="52" t="s">
-        <v>237</v>
-      </c>
-      <c r="E2" s="67" t="s">
-        <v>360</v>
-      </c>
-      <c r="F2" s="52" t="s">
-        <v>330</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" xr:uid="{1A197657-F570-4A6C-95EA-50684754A62C}"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
